--- a/Database/Data.xlsx
+++ b/Database/Data.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/867b96fdabfe5cc4/Ubuntu/CongNghePhanMem/ThucHanh/CSDL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hnm08\OneDrive\Ubuntu\CongNghePhanMem\BookStoreManagement\Database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{4B65B971-8DF4-4F2B-B95E-CB8165BD283E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE437BFB-F69D-4642-B673-DDADF415C205}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Account" sheetId="2" r:id="rId1"/>
@@ -21,7 +20,7 @@
     <sheet name="Publisher" sheetId="6" r:id="rId6"/>
     <sheet name="Book" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,12 +38,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -63,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +78,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -108,12 +107,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -156,12 +155,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -179,7 +178,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000002000000}">
+    <comment ref="B1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -195,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0800-000003000000}">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -221,12 +220,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -253,12 +252,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
+    <comment ref="A1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -274,7 +273,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -290,7 +289,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -306,7 +305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{134A4014-CE2A-455E-8426-D70CF8A11A23}">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -322,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{0916B588-1EE1-4733-A2B0-9DB3CC33DB4A}">
+    <comment ref="G1" authorId="0" shapeId="0">
       <text>
         <r>
           <rPr>
@@ -348,7 +347,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="441">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="438">
   <si>
     <t>Name</t>
   </si>
@@ -1605,15 +1604,6 @@
   </si>
   <si>
     <t>SID05</t>
-  </si>
-  <si>
-    <t>454646</t>
-  </si>
-  <si>
-    <t>2077035</t>
-  </si>
-  <si>
-    <t>329565</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Huyền</t>
@@ -1676,8 +1666,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1778,6 +1768,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1800,7 +1796,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1815,11 +1811,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1832,6 +1824,7 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2075,13 +2068,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H1002"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
     <col min="2" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="4" width="8.625" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="19.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.375" bestFit="1" customWidth="1"/>
@@ -2116,23 +2110,24 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="11" t="str">
+      <c r="B2" s="10" t="str">
         <f>A2&amp;D2</f>
         <v>SID01staff</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="D2" s="13" t="s">
+      <c r="C2" s="23" t="str">
+        <f>A2&amp;"@"&amp;D2</f>
+        <v>SID01@staff</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>355</v>
       </c>
       <c r="G2" t="s">
@@ -2143,23 +2138,24 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="B3" s="11" t="str">
+      <c r="B3" s="10" t="str">
         <f t="shared" ref="B3:B13" si="0">A3&amp;D3</f>
         <v>SID02staff</v>
       </c>
-      <c r="C3" s="11">
-        <v>533292</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="C3" s="23" t="str">
+        <f t="shared" ref="C3:C13" si="1">A3&amp;"@"&amp;D3</f>
+        <v>SID02@staff</v>
+      </c>
+      <c r="D3" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>356</v>
       </c>
       <c r="G3" t="s">
@@ -2170,77 +2166,80 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="11" t="str">
+      <c r="B4" s="10" t="str">
         <f t="shared" si="0"/>
         <v>SID03staff</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>SID03@staff</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>419</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>422</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>424</v>
+      <c r="F4" s="10" t="s">
+        <v>421</v>
       </c>
       <c r="G4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>428</v>
+        <v>423</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>425</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="B5" s="11" t="str">
+      <c r="B5" s="10" t="str">
         <f t="shared" si="0"/>
         <v>SID04staff</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>421</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>SID04@staff</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E5" s="20" t="s">
-        <v>423</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>425</v>
+      <c r="E5" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>422</v>
       </c>
       <c r="G5" t="s">
-        <v>427</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>429</v>
+        <v>424</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="B6" s="11" t="str">
+      <c r="B6" s="10" t="str">
         <f t="shared" si="0"/>
         <v>SID05staff</v>
       </c>
-      <c r="C6" s="11">
-        <v>918511</v>
-      </c>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>SID05@staff</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="10" t="s">
         <v>357</v>
       </c>
       <c r="G6" t="s">
@@ -2251,23 +2250,24 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="11" t="str">
+      <c r="B7" s="10" t="str">
         <f t="shared" si="0"/>
         <v>CID01client</v>
       </c>
-      <c r="C7" s="11">
-        <v>150226</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>CID01@client</v>
+      </c>
+      <c r="D7" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="10" t="s">
         <v>358</v>
       </c>
       <c r="G7" t="s">
@@ -2278,23 +2278,24 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="B8" s="11" t="str">
+      <c r="B8" s="10" t="str">
         <f t="shared" si="0"/>
         <v>CID02client</v>
       </c>
-      <c r="C8" s="11">
-        <v>938302</v>
-      </c>
-      <c r="D8" s="13" t="s">
+      <c r="C8" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>CID02@client</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E8" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="10" t="s">
         <v>359</v>
       </c>
       <c r="G8" t="s">
@@ -2305,23 +2306,24 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="11" t="str">
+      <c r="B9" s="10" t="str">
         <f t="shared" si="0"/>
         <v>CID03client</v>
       </c>
-      <c r="C9" s="11">
-        <v>411896</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="C9" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>CID03@client</v>
+      </c>
+      <c r="D9" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="10" t="s">
         <v>360</v>
       </c>
       <c r="G9" t="s">
@@ -2332,23 +2334,24 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="B10" s="11" t="str">
+      <c r="B10" s="10" t="str">
         <f t="shared" si="0"/>
         <v>CID04client</v>
       </c>
-      <c r="C10" s="11">
-        <v>396778</v>
-      </c>
-      <c r="D10" s="13" t="s">
+      <c r="C10" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>CID04@client</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="10" t="s">
         <v>361</v>
       </c>
       <c r="G10" t="s">
@@ -2359,23 +2362,24 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="11" t="str">
+      <c r="B11" s="10" t="str">
         <f t="shared" si="0"/>
         <v>CID05client</v>
       </c>
-      <c r="C11" s="12">
-        <v>497644</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="C11" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>CID05@client</v>
+      </c>
+      <c r="D11" s="11" t="s">
         <v>33</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="10" t="s">
         <v>362</v>
       </c>
       <c r="G11" t="s">
@@ -2386,23 +2390,24 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="11" t="str">
+      <c r="B12" s="10" t="str">
         <f t="shared" si="0"/>
         <v>AID01admin</v>
       </c>
-      <c r="C12" s="11">
-        <v>806967</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="C12" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>AID01@admin</v>
+      </c>
+      <c r="D12" s="11" t="s">
         <v>39</v>
       </c>
       <c r="E12" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="10" t="s">
         <v>363</v>
       </c>
       <c r="G12" t="s">
@@ -2413,23 +2418,24 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="11" t="str">
+      <c r="B13" s="10" t="str">
         <f t="shared" si="0"/>
         <v>AID02admin</v>
       </c>
-      <c r="C13" s="11">
-        <v>144107</v>
-      </c>
-      <c r="D13" s="13" t="s">
+      <c r="C13" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>AID02@admin</v>
+      </c>
+      <c r="D13" s="11" t="s">
         <v>39</v>
       </c>
       <c r="E13" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="10" t="s">
         <v>364</v>
       </c>
       <c r="G13" t="s">
@@ -3431,8 +3437,8 @@
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H4" r:id="rId1" xr:uid="{152AB56E-BB48-46D6-BE76-D6FDECB61D5A}"/>
-    <hyperlink ref="H5" r:id="rId2" xr:uid="{5EDC980F-0D3C-435C-A0DB-1DA6E7F798B1}"/>
+    <hyperlink ref="H4" r:id="rId1"/>
+    <hyperlink ref="H5" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId3"/>
@@ -3441,7 +3447,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{968085CA-8F9F-460C-B239-EA71A58634D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3451,13 +3457,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>42</v>
@@ -3471,12 +3477,12 @@
         <v>7360000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="D2" s="21">
+        <v>432</v>
+      </c>
+      <c r="D2" s="19">
         <v>45174</v>
       </c>
-      <c r="E2" s="23"/>
+      <c r="E2" s="21"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -3486,12 +3492,12 @@
         <v>6430000</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D3" s="21">
+        <v>431</v>
+      </c>
+      <c r="D3" s="19">
         <v>45107</v>
       </c>
-      <c r="E3" s="23"/>
+      <c r="E3" s="21"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -3501,12 +3507,12 @@
         <v>4780000</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="22">
+        <v>430</v>
+      </c>
+      <c r="D4" s="20">
         <v>45091</v>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3516,12 +3522,12 @@
         <v>4540000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>433</v>
-      </c>
-      <c r="D5" s="21">
+        <v>430</v>
+      </c>
+      <c r="D5" s="19">
         <v>44955</v>
       </c>
-      <c r="E5" s="23"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3531,15 +3537,15 @@
         <v>7160000</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>435</v>
-      </c>
-      <c r="D6" s="21">
+        <v>432</v>
+      </c>
+      <c r="D6" s="19">
         <v>45048</v>
       </c>
-      <c r="E6" s="23"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="11" t="s">
         <v>38</v>
       </c>
       <c r="B7">
@@ -3548,13 +3554,13 @@
       <c r="C7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="19">
         <v>44954</v>
       </c>
-      <c r="E7" s="23"/>
+      <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="11" t="s">
         <v>40</v>
       </c>
       <c r="B8">
@@ -3563,10 +3569,10 @@
       <c r="C8" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="21">
+      <c r="D8" s="19">
         <v>44932</v>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3574,7 +3580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3594,8 +3600,8 @@
       <c r="C1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="24" t="s">
-        <v>437</v>
+      <c r="D1" s="22" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3609,7 +3615,7 @@
         <v>44885</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3623,7 +3629,7 @@
         <v>44886</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3637,7 +3643,7 @@
         <v>44887</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3651,7 +3657,7 @@
         <v>44888</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3665,7 +3671,7 @@
         <v>44889</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3679,7 +3685,7 @@
         <v>44890</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3693,7 +3699,7 @@
         <v>44891</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3707,7 +3713,7 @@
         <v>44892</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3721,7 +3727,7 @@
         <v>44893</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3735,7 +3741,7 @@
         <v>44894</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3749,7 +3755,7 @@
         <v>44895</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3763,7 +3769,7 @@
         <v>44896</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3777,7 +3783,7 @@
         <v>44897</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3791,7 +3797,7 @@
         <v>44898</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3805,7 +3811,7 @@
         <v>44899</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3819,7 +3825,7 @@
         <v>44900</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3833,7 +3839,7 @@
         <v>44901</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3847,7 +3853,7 @@
         <v>44902</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3861,7 +3867,7 @@
         <v>44903</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3875,7 +3881,7 @@
         <v>44904</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3889,7 +3895,7 @@
         <v>44905</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3903,7 +3909,7 @@
         <v>44906</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3917,7 +3923,7 @@
         <v>44907</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3931,7 +3937,7 @@
         <v>44908</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3945,7 +3951,7 @@
         <v>44909</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3959,7 +3965,7 @@
         <v>44910</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3973,7 +3979,7 @@
         <v>44911</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3987,7 +3993,7 @@
         <v>44912</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4001,7 +4007,7 @@
         <v>44913</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4015,7 +4021,7 @@
         <v>44914</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4029,7 +4035,7 @@
         <v>44915</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4043,7 +4049,7 @@
         <v>44916</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4057,7 +4063,7 @@
         <v>44917</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4071,7 +4077,7 @@
         <v>44918</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4085,7 +4091,7 @@
         <v>44919</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4099,7 +4105,7 @@
         <v>44920</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4113,7 +4119,7 @@
         <v>44921</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4127,7 +4133,7 @@
         <v>44922</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4141,7 +4147,7 @@
         <v>44923</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -4155,7 +4161,7 @@
         <v>44924</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5174,7 +5180,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1006"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -7116,7 +7122,7 @@
     <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A80">
+  <sortState ref="A2:A80">
     <sortCondition ref="A2:A80"/>
   </sortState>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -7127,7 +7133,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -7155,7 +7161,7 @@
       <c r="B2" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="15" t="s">
         <v>375</v>
       </c>
     </row>
@@ -7166,7 +7172,7 @@
       <c r="B3" t="s">
         <v>87</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="16" t="s">
         <v>376</v>
       </c>
     </row>
@@ -7177,7 +7183,7 @@
       <c r="B4" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="16" t="s">
         <v>377</v>
       </c>
     </row>
@@ -7188,7 +7194,7 @@
       <c r="B5" t="s">
         <v>91</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="16" t="s">
         <v>378</v>
       </c>
     </row>
@@ -7199,7 +7205,7 @@
       <c r="B6" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="16" t="s">
         <v>379</v>
       </c>
     </row>
@@ -7210,7 +7216,7 @@
       <c r="B7" t="s">
         <v>95</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="16" t="s">
         <v>380</v>
       </c>
     </row>
@@ -7221,7 +7227,7 @@
       <c r="B8" t="s">
         <v>97</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="16" t="s">
         <v>381</v>
       </c>
     </row>
@@ -7232,7 +7238,7 @@
       <c r="B9" t="s">
         <v>99</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="16" t="s">
         <v>382</v>
       </c>
     </row>
@@ -7243,7 +7249,7 @@
       <c r="B10" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="16" t="s">
         <v>383</v>
       </c>
     </row>
@@ -7254,7 +7260,7 @@
       <c r="B11" t="s">
         <v>103</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="16" t="s">
         <v>384</v>
       </c>
     </row>
@@ -7265,7 +7271,7 @@
       <c r="B12" t="s">
         <v>105</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="16" t="s">
         <v>385</v>
       </c>
     </row>
@@ -7276,7 +7282,7 @@
       <c r="B13" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="16" t="s">
         <v>386</v>
       </c>
     </row>
@@ -7287,7 +7293,7 @@
       <c r="B14" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="16" t="s">
         <v>387</v>
       </c>
     </row>
@@ -7298,7 +7304,7 @@
       <c r="B15" t="s">
         <v>111</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="16" t="s">
         <v>388</v>
       </c>
     </row>
@@ -7309,7 +7315,7 @@
       <c r="B16" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="16" t="s">
         <v>389</v>
       </c>
     </row>
@@ -7320,7 +7326,7 @@
       <c r="B17" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="17" t="s">
         <v>390</v>
       </c>
     </row>
@@ -7331,7 +7337,7 @@
       <c r="B18" t="s">
         <v>117</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="17" t="s">
         <v>391</v>
       </c>
     </row>
@@ -7342,7 +7348,7 @@
       <c r="B19" t="s">
         <v>119</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="17" t="s">
         <v>392</v>
       </c>
     </row>
@@ -7350,10 +7356,10 @@
       <c r="A20" t="s">
         <v>120</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="17" t="s">
         <v>393</v>
       </c>
     </row>
@@ -7364,7 +7370,7 @@
       <c r="B21" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="17" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7375,7 +7381,7 @@
       <c r="B22" t="s">
         <v>125</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="17" t="s">
         <v>395</v>
       </c>
     </row>
@@ -7386,7 +7392,7 @@
       <c r="B23" t="s">
         <v>127</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="17" t="s">
         <v>396</v>
       </c>
     </row>
@@ -8375,7 +8381,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8414,7 +8420,7 @@
       <c r="B3" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="C3" s="13" t="s">
         <v>142</v>
       </c>
     </row>
@@ -8425,7 +8431,7 @@
       <c r="B4" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="13" t="s">
         <v>145</v>
       </c>
     </row>
@@ -8436,7 +8442,7 @@
       <c r="B5" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="14" t="s">
         <v>148</v>
       </c>
     </row>
@@ -8447,7 +8453,7 @@
       <c r="B6" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="14" t="s">
         <v>151</v>
       </c>
     </row>
@@ -8458,7 +8464,7 @@
       <c r="B7" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="14" t="s">
         <v>154</v>
       </c>
     </row>
@@ -8469,7 +8475,7 @@
       <c r="B8" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="14" t="s">
         <v>157</v>
       </c>
     </row>
@@ -8480,7 +8486,7 @@
       <c r="B9" t="s">
         <v>159</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="14" t="s">
         <v>160</v>
       </c>
     </row>
@@ -8491,7 +8497,7 @@
       <c r="B10" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="14" t="s">
         <v>163</v>
       </c>
     </row>
@@ -8502,7 +8508,7 @@
       <c r="B11" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="14" t="s">
         <v>166</v>
       </c>
     </row>
@@ -8513,7 +8519,7 @@
       <c r="B12" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="14" t="s">
         <v>169</v>
       </c>
     </row>
@@ -8524,7 +8530,7 @@
       <c r="B13" t="s">
         <v>171</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="14" t="s">
         <v>172</v>
       </c>
     </row>
@@ -8535,7 +8541,7 @@
       <c r="B14" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="14" t="s">
         <v>175</v>
       </c>
     </row>
@@ -8546,7 +8552,7 @@
       <c r="B15" t="s">
         <v>177</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="14" t="s">
         <v>178</v>
       </c>
     </row>
@@ -11507,19 +11513,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
-    <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
-    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
-    <hyperlink ref="C6" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
-    <hyperlink ref="C7" r:id="rId5" xr:uid="{52B869BB-B5D3-4A67-9A6C-2BE3BDA4FC68}"/>
-    <hyperlink ref="C8" r:id="rId6" xr:uid="{9693602D-AD4F-49FE-8436-6EE3EAD4EADE}"/>
-    <hyperlink ref="C9" r:id="rId7" xr:uid="{BA0F86A9-3FBC-48A3-A10D-D0CC0F5DDA5B}"/>
-    <hyperlink ref="C10" r:id="rId8" xr:uid="{F0BBCA88-6FC9-4473-AB92-155662699F96}"/>
-    <hyperlink ref="C11" r:id="rId9" xr:uid="{B7AD6B10-153B-4CFB-917E-A58FB264E283}"/>
-    <hyperlink ref="C12" r:id="rId10" xr:uid="{685E8F8D-1E69-46FD-A4C1-C5C53B2AC873}"/>
-    <hyperlink ref="C13" r:id="rId11" xr:uid="{C1F21F50-463D-477B-BEC9-6AD05CC70AF1}"/>
-    <hyperlink ref="C14" r:id="rId12" xr:uid="{B1C384CB-8740-4CA4-8BEC-56B8E5685A4C}"/>
-    <hyperlink ref="C15" r:id="rId13" xr:uid="{72A53EE1-1014-455E-B279-01A53873E625}"/>
+    <hyperlink ref="C3" r:id="rId1"/>
+    <hyperlink ref="C4" r:id="rId2"/>
+    <hyperlink ref="C5" r:id="rId3"/>
+    <hyperlink ref="C6" r:id="rId4"/>
+    <hyperlink ref="C7" r:id="rId5"/>
+    <hyperlink ref="C8" r:id="rId6"/>
+    <hyperlink ref="C9" r:id="rId7"/>
+    <hyperlink ref="C10" r:id="rId8"/>
+    <hyperlink ref="C11" r:id="rId9"/>
+    <hyperlink ref="C12" r:id="rId10"/>
+    <hyperlink ref="C13" r:id="rId11"/>
+    <hyperlink ref="C14" r:id="rId12"/>
+    <hyperlink ref="C15" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11527,7 +11533,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -11553,7 +11559,7 @@
         <v>134</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>353</v>

--- a/Database/Data.xlsx
+++ b/Database/Data.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hnm08\OneDrive\Ubuntu\CongNghePhanMem\BookStoreManagement\Database\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/867b96fdabfe5cc4/Ubuntu/CongNghePhanMem/BookStoreManagement/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_8FEB9D8DC7A054F8B33F543BBE935DD73E6C2F80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3F26B9-6938-4A83-93E2-B97CF488406E}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Account" sheetId="2" r:id="rId1"/>
@@ -20,7 +21,7 @@
     <sheet name="Publisher" sheetId="6" r:id="rId6"/>
     <sheet name="Book" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,12 +39,12 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -62,7 +63,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -78,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -107,12 +108,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -129,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -155,12 +156,12 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -178,7 +179,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -194,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -220,12 +221,12 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -252,12 +253,12 @@
 </file>
 
 <file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -273,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -289,7 +290,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -305,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -321,7 +322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -347,7 +348,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="459">
   <si>
     <t>Name</t>
   </si>
@@ -433,303 +434,87 @@
     <t>Type</t>
   </si>
   <si>
-    <t>SID01</t>
-  </si>
-  <si>
     <t>staff</t>
   </si>
   <si>
-    <t>SID02</t>
-  </si>
-  <si>
-    <t>SID03</t>
-  </si>
-  <si>
-    <t>CID01</t>
-  </si>
-  <si>
     <t>client</t>
   </si>
   <si>
-    <t>CID02</t>
-  </si>
-  <si>
-    <t>CID03</t>
-  </si>
-  <si>
-    <t>CID04</t>
-  </si>
-  <si>
-    <t>CID05</t>
-  </si>
-  <si>
-    <t>AID01</t>
-  </si>
-  <si>
     <t>admin</t>
   </si>
   <si>
-    <t>AID02</t>
-  </si>
-  <si>
     <t>BillID</t>
   </si>
   <si>
     <t>Date</t>
   </si>
   <si>
-    <t>BiID01</t>
-  </si>
-  <si>
-    <t>BiID02</t>
-  </si>
-  <si>
-    <t>BiID03</t>
-  </si>
-  <si>
-    <t>BiID04</t>
-  </si>
-  <si>
-    <t>BiID05</t>
-  </si>
-  <si>
-    <t>BiID06</t>
-  </si>
-  <si>
-    <t>BiID07</t>
-  </si>
-  <si>
-    <t>BiID08</t>
-  </si>
-  <si>
-    <t>BiID09</t>
-  </si>
-  <si>
-    <t>BiID10</t>
-  </si>
-  <si>
-    <t>BiID11</t>
-  </si>
-  <si>
-    <t>BiID12</t>
-  </si>
-  <si>
-    <t>BiID13</t>
-  </si>
-  <si>
-    <t>BiID14</t>
-  </si>
-  <si>
-    <t>BiID15</t>
-  </si>
-  <si>
-    <t>BiID16</t>
-  </si>
-  <si>
-    <t>BiID17</t>
-  </si>
-  <si>
-    <t>BiID18</t>
-  </si>
-  <si>
-    <t>BiID19</t>
-  </si>
-  <si>
-    <t>BiID20</t>
-  </si>
-  <si>
-    <t>BiID21</t>
-  </si>
-  <si>
-    <t>BiID22</t>
-  </si>
-  <si>
-    <t>BiID23</t>
-  </si>
-  <si>
-    <t>BiID24</t>
-  </si>
-  <si>
-    <t>BiID25</t>
-  </si>
-  <si>
-    <t>BiID26</t>
-  </si>
-  <si>
-    <t>BiID27</t>
-  </si>
-  <si>
-    <t>BiID28</t>
-  </si>
-  <si>
-    <t>BiID29</t>
-  </si>
-  <si>
-    <t>BiID30</t>
-  </si>
-  <si>
-    <t>BiID31</t>
-  </si>
-  <si>
-    <t>BiID32</t>
-  </si>
-  <si>
-    <t>BiID33</t>
-  </si>
-  <si>
-    <t>BiID34</t>
-  </si>
-  <si>
-    <t>BiID35</t>
-  </si>
-  <si>
-    <t>BiID36</t>
-  </si>
-  <si>
-    <t>BiID37</t>
-  </si>
-  <si>
-    <t>BiID38</t>
-  </si>
-  <si>
-    <t>BiID39</t>
-  </si>
-  <si>
-    <t>BiID40</t>
-  </si>
-  <si>
     <t>AuthorID</t>
   </si>
   <si>
-    <t>AuID01</t>
-  </si>
-  <si>
     <t>Acacia</t>
   </si>
   <si>
-    <t>AuID02</t>
-  </si>
-  <si>
     <t>Adela</t>
   </si>
   <si>
-    <t>AuID03</t>
-  </si>
-  <si>
     <t>Elfleda</t>
   </si>
   <si>
-    <t>AuID04</t>
-  </si>
-  <si>
     <t>Adelaide</t>
   </si>
   <si>
-    <t>AuID05</t>
-  </si>
-  <si>
     <t>Doris</t>
   </si>
   <si>
-    <t>AuID06</t>
-  </si>
-  <si>
     <t>Blanche</t>
   </si>
   <si>
-    <t>AuID07</t>
-  </si>
-  <si>
     <t>Fidelia</t>
   </si>
   <si>
-    <t>AuID08</t>
-  </si>
-  <si>
     <t>Genevieve</t>
   </si>
   <si>
-    <t>AuID09</t>
-  </si>
-  <si>
     <t>Helga</t>
   </si>
   <si>
-    <t>AuID10</t>
-  </si>
-  <si>
     <t>Imelda</t>
   </si>
   <si>
-    <t>AuID11</t>
-  </si>
-  <si>
     <t>Jezebel</t>
   </si>
   <si>
-    <t>AuID12</t>
-  </si>
-  <si>
     <t>Joyce</t>
   </si>
   <si>
-    <t>AuID13</t>
-  </si>
-  <si>
     <t>Kaylin</t>
   </si>
   <si>
-    <t>AuID14</t>
-  </si>
-  <si>
     <t>Ladonna</t>
   </si>
   <si>
-    <t>AuID15</t>
-  </si>
-  <si>
     <t>Mabel</t>
   </si>
   <si>
-    <t>AuID17</t>
-  </si>
-  <si>
     <t>HPNM</t>
   </si>
   <si>
-    <t>AuID18</t>
-  </si>
-  <si>
     <t>AnnaThang</t>
   </si>
   <si>
-    <t>AuID19</t>
-  </si>
-  <si>
     <t>Phạm Hải</t>
   </si>
   <si>
-    <t>AuID20</t>
-  </si>
-  <si>
     <t>Aoyama Gōshō</t>
   </si>
   <si>
-    <t>AuID21</t>
-  </si>
-  <si>
     <t>Team Teacher</t>
   </si>
   <si>
-    <t>AuID22</t>
-  </si>
-  <si>
     <t>Team IT</t>
   </si>
   <si>
-    <t>AuID23</t>
-  </si>
-  <si>
     <t>War Earth</t>
   </si>
   <si>
@@ -760,126 +545,84 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>PID01</t>
-  </si>
-  <si>
     <t>NXB Đại học Quốc gia</t>
   </si>
   <si>
     <t>0878781202</t>
   </si>
   <si>
-    <t>PID02</t>
-  </si>
-  <si>
     <t>NXB Sự thật</t>
   </si>
   <si>
     <t>suthat123@gmail.com</t>
   </si>
   <si>
-    <t>PID03</t>
-  </si>
-  <si>
     <t>NXB Kim Đồng</t>
   </si>
   <si>
     <t>kimdongbacvang@email.com</t>
   </si>
   <si>
-    <t>PID04</t>
-  </si>
-  <si>
     <t>NXB Giáo Dục</t>
   </si>
   <si>
     <t>giaoduc@edu.com.vn</t>
   </si>
   <si>
-    <t>PID05</t>
-  </si>
-  <si>
     <t xml:space="preserve">NXB Thanh Niên </t>
   </si>
   <si>
     <t>ThanhnienVN@gmail.com</t>
   </si>
   <si>
-    <t>PID06</t>
-  </si>
-  <si>
     <t>NXB KHTN &amp; CN</t>
   </si>
   <si>
     <t>khtnvacongnghe@gmail.com</t>
   </si>
   <si>
-    <t>PID07</t>
-  </si>
-  <si>
     <t>NXB The Universe</t>
   </si>
   <si>
     <t>world@space.earth.com</t>
   </si>
   <si>
-    <t>PID08</t>
-  </si>
-  <si>
     <t>NXB Thế Giới</t>
   </si>
   <si>
     <t>thegioi132@gmail.com</t>
   </si>
   <si>
-    <t>PID09</t>
-  </si>
-  <si>
     <t>NXB CHiến Tranh</t>
   </si>
   <si>
     <t>war@gmail.com</t>
   </si>
   <si>
-    <t>PID10</t>
-  </si>
-  <si>
     <t>RELX Group</t>
   </si>
   <si>
     <t>relxgr@gmail.com</t>
   </si>
   <si>
-    <t>PID11</t>
-  </si>
-  <si>
     <t>Hachette Livre</t>
   </si>
   <si>
     <t>hlivre@gmail.com</t>
   </si>
   <si>
-    <t>PID12</t>
-  </si>
-  <si>
     <t>Springer Nature</t>
   </si>
   <si>
     <t>Snature1@gmail.com</t>
   </si>
   <si>
-    <t>PID13</t>
-  </si>
-  <si>
     <t>McGraw-Hill Education</t>
   </si>
   <si>
     <t>mghilledu@edu.com.vn</t>
   </si>
   <si>
-    <t>PID14</t>
-  </si>
-  <si>
     <t>NXB Trung Quốc</t>
   </si>
   <si>
@@ -892,519 +635,261 @@
     <t>BookName</t>
   </si>
   <si>
-    <t>BID01</t>
-  </si>
-  <si>
     <t>Norwegian wood</t>
   </si>
   <si>
-    <t>BID02</t>
-  </si>
-  <si>
     <t>To kill a mockingbird</t>
   </si>
   <si>
-    <t>BID03</t>
-  </si>
-  <si>
     <t>The Alchemist</t>
   </si>
   <si>
-    <t>BID04</t>
-  </si>
-  <si>
     <t>Life Of Pi</t>
   </si>
   <si>
-    <t>BID05</t>
-  </si>
-  <si>
     <t>Diary Of A Wimpy Kid</t>
   </si>
   <si>
-    <t>BID06</t>
-  </si>
-  <si>
     <t>To Kill A Mockingbird</t>
   </si>
   <si>
-    <t>BID07</t>
-  </si>
-  <si>
     <t>Wonder</t>
   </si>
   <si>
-    <t>BID08</t>
-  </si>
-  <si>
     <t>Moby Dick</t>
   </si>
   <si>
-    <t>BID09</t>
-  </si>
-  <si>
     <t>Peter Pan</t>
   </si>
   <si>
-    <t>BID10</t>
-  </si>
-  <si>
     <t>Madame Bovary</t>
   </si>
   <si>
-    <t>BID11</t>
-  </si>
-  <si>
     <t>Dear John</t>
   </si>
   <si>
-    <t>BID12</t>
-  </si>
-  <si>
     <t>Me Before You</t>
   </si>
   <si>
-    <t>BID13</t>
-  </si>
-  <si>
     <t>Thirteen Reasons Why</t>
   </si>
   <si>
-    <t>BID14</t>
-  </si>
-  <si>
     <t>Tuesdays with Morrie</t>
   </si>
   <si>
-    <t>BID15</t>
-  </si>
-  <si>
     <t xml:space="preserve">Alice’s adventures in wonderland </t>
   </si>
   <si>
-    <t>BID16</t>
-  </si>
-  <si>
     <t>Conan</t>
   </si>
   <si>
-    <t>BID17</t>
-  </si>
-  <si>
     <t>Toán 1</t>
   </si>
   <si>
-    <t>BID18</t>
-  </si>
-  <si>
     <t>Toán 2</t>
   </si>
   <si>
-    <t>BID19</t>
-  </si>
-  <si>
     <t>Toán 3</t>
   </si>
   <si>
-    <t>BID20</t>
-  </si>
-  <si>
     <t>Toán 4</t>
   </si>
   <si>
-    <t>BID21</t>
-  </si>
-  <si>
     <t>Toán 5</t>
   </si>
   <si>
-    <t>BID22</t>
-  </si>
-  <si>
     <t>Toán 6</t>
   </si>
   <si>
-    <t>BID23</t>
-  </si>
-  <si>
     <t>Toán 7</t>
   </si>
   <si>
-    <t>BID24</t>
-  </si>
-  <si>
     <t>Toán 8</t>
   </si>
   <si>
-    <t>BID25</t>
-  </si>
-  <si>
     <t>Toán 9</t>
   </si>
   <si>
-    <t>BID26</t>
-  </si>
-  <si>
     <t>Toán 10</t>
   </si>
   <si>
-    <t>BID27</t>
-  </si>
-  <si>
     <t>Toán 11</t>
   </si>
   <si>
-    <t>BID28</t>
-  </si>
-  <si>
     <t>Toán 12</t>
   </si>
   <si>
-    <t>BID29</t>
-  </si>
-  <si>
     <t>Văn 1</t>
   </si>
   <si>
-    <t>BID30</t>
-  </si>
-  <si>
     <t>Văn 2</t>
   </si>
   <si>
-    <t>BID31</t>
-  </si>
-  <si>
     <t>Văn 3</t>
   </si>
   <si>
-    <t>BID32</t>
-  </si>
-  <si>
     <t>Văn 4</t>
   </si>
   <si>
-    <t>BID33</t>
-  </si>
-  <si>
     <t>Văn 5</t>
   </si>
   <si>
-    <t>BID34</t>
-  </si>
-  <si>
     <t>Văn 6</t>
   </si>
   <si>
-    <t>BID35</t>
-  </si>
-  <si>
     <t>Văn 7</t>
   </si>
   <si>
-    <t>BID36</t>
-  </si>
-  <si>
     <t>Văn 8</t>
   </si>
   <si>
-    <t>BID37</t>
-  </si>
-  <si>
     <t>Văn 9</t>
   </si>
   <si>
-    <t>BID38</t>
-  </si>
-  <si>
     <t>Văn 10</t>
   </si>
   <si>
-    <t>BID39</t>
-  </si>
-  <si>
     <t>Văn 11</t>
   </si>
   <si>
-    <t>BID40</t>
-  </si>
-  <si>
     <t>Văn 12</t>
   </si>
   <si>
-    <t>BID41</t>
-  </si>
-  <si>
     <t>English 1</t>
   </si>
   <si>
-    <t>BID42</t>
-  </si>
-  <si>
     <t>English 2</t>
   </si>
   <si>
-    <t>BID43</t>
-  </si>
-  <si>
     <t>English 3</t>
   </si>
   <si>
-    <t>BID44</t>
-  </si>
-  <si>
     <t>English 4</t>
   </si>
   <si>
-    <t>BID45</t>
-  </si>
-  <si>
     <t>English 5</t>
   </si>
   <si>
-    <t>BID46</t>
-  </si>
-  <si>
     <t>English 6</t>
   </si>
   <si>
-    <t>BID47</t>
-  </si>
-  <si>
     <t>English 7</t>
   </si>
   <si>
-    <t>BID48</t>
-  </si>
-  <si>
     <t>English 8</t>
   </si>
   <si>
-    <t>BID49</t>
-  </si>
-  <si>
     <t>English 9</t>
   </si>
   <si>
-    <t>BID50</t>
-  </si>
-  <si>
     <t>English 10</t>
   </si>
   <si>
-    <t>BID51</t>
-  </si>
-  <si>
     <t>English 11</t>
   </si>
   <si>
-    <t>BID52</t>
-  </si>
-  <si>
     <t>English 12</t>
   </si>
   <si>
-    <t>BID53</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 1</t>
   </si>
   <si>
-    <t>BID54</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 2</t>
   </si>
   <si>
-    <t>BID55</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 3</t>
   </si>
   <si>
-    <t>BID56</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 4</t>
   </si>
   <si>
-    <t>BID57</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 5</t>
   </si>
   <si>
-    <t>BID58</t>
-  </si>
-  <si>
     <t>Công nghệ phần mềm 6</t>
   </si>
   <si>
-    <t>BID59</t>
-  </si>
-  <si>
     <t>C++ dev</t>
   </si>
   <si>
-    <t>BID60</t>
-  </si>
-  <si>
     <t>Python</t>
   </si>
   <si>
-    <t>BID61</t>
-  </si>
-  <si>
     <t>Java Book</t>
   </si>
   <si>
-    <t>BID62</t>
-  </si>
-  <si>
     <t>Artificial Intelligence</t>
   </si>
   <si>
-    <t>BID63</t>
-  </si>
-  <si>
     <t>Tớ học lập trình</t>
   </si>
   <si>
-    <t>BID64</t>
-  </si>
-  <si>
     <t>Kiến trúc máy tính</t>
   </si>
   <si>
-    <t>BID65</t>
-  </si>
-  <si>
     <t>Chinh phục lập trình</t>
   </si>
   <si>
-    <t>BID66</t>
-  </si>
-  <si>
     <t>Giải tích 1</t>
   </si>
   <si>
-    <t>BID67</t>
-  </si>
-  <si>
     <t>Giải tích 2</t>
   </si>
   <si>
-    <t>BID68</t>
-  </si>
-  <si>
     <t>Giải tích 3</t>
   </si>
   <si>
-    <t>BID69</t>
-  </si>
-  <si>
     <t>Giải tích 4</t>
   </si>
   <si>
-    <t>BID70</t>
-  </si>
-  <si>
     <t>Lịch Sử Tổng Hợp 1</t>
   </si>
   <si>
-    <t>BID71</t>
-  </si>
-  <si>
     <t>Sinh Học Tế bào</t>
   </si>
   <si>
-    <t>BID72</t>
-  </si>
-  <si>
     <t>Công nghệ Sinh Học</t>
   </si>
   <si>
-    <t>BID73</t>
-  </si>
-  <si>
     <t>Hóa sinh Cơ bản</t>
   </si>
   <si>
-    <t>BID74</t>
-  </si>
-  <si>
     <t>Đột phá tư duy 1</t>
   </si>
   <si>
-    <t>BID75</t>
-  </si>
-  <si>
     <t>Đột phá tư duy 2</t>
   </si>
   <si>
-    <t>BID76</t>
-  </si>
-  <si>
     <t>Đột phá tư duy 3</t>
   </si>
   <si>
-    <t>BID77</t>
-  </si>
-  <si>
     <t>Bách Khoa Toàn Thư</t>
   </si>
   <si>
-    <t>BID78</t>
-  </si>
-  <si>
     <t>Bí Ẩn Vũ Trụ - Bí ẩn 3 6 9</t>
   </si>
   <si>
-    <t>BID79</t>
-  </si>
-  <si>
     <t>Xuyên Không Thời Gian</t>
   </si>
   <si>
-    <t>BID80</t>
-  </si>
-  <si>
     <t>Chiến Tranh Thế Giới 2 3</t>
   </si>
   <si>
-    <t>BID81</t>
-  </si>
-  <si>
     <t>Công Nghiệp Hóa Toàn Cầu</t>
   </si>
   <si>
-    <t>BID82</t>
-  </si>
-  <si>
     <t>Ultimate Human</t>
   </si>
   <si>
-    <t>BID83</t>
-  </si>
-  <si>
     <t>Relax Time</t>
   </si>
   <si>
-    <t>BID84</t>
-  </si>
-  <si>
     <t>The Eyes</t>
   </si>
   <si>
-    <t>BID85</t>
-  </si>
-  <si>
     <t>Iphone 11 Series</t>
   </si>
   <si>
-    <t>BID86</t>
-  </si>
-  <si>
     <t>How To Creat EveryThings</t>
   </si>
   <si>
@@ -1600,12 +1085,6 @@
     <t>Sách không dành cho người thường</t>
   </si>
   <si>
-    <t>SID04</t>
-  </si>
-  <si>
-    <t>SID05</t>
-  </si>
-  <si>
     <t>Nguyễn Ngọc Huyền</t>
   </si>
   <si>
@@ -1661,12 +1140,597 @@
   </si>
   <si>
     <t>delivery</t>
+  </si>
+  <si>
+    <t>118 Cống Quỳnh, Tp HCM</t>
+  </si>
+  <si>
+    <t>Đinh Bá Tùng</t>
+  </si>
+  <si>
+    <t>0818704548</t>
+  </si>
+  <si>
+    <t>dinhbatung_UID01@gmail.com</t>
+  </si>
+  <si>
+    <t>290 Hồ Văn Huê, Tp HCM</t>
+  </si>
+  <si>
+    <t>Lê Quỳnh Nhung</t>
+  </si>
+  <si>
+    <t>0871171036</t>
+  </si>
+  <si>
+    <t>lequynhnhung_UID04@gmail.com</t>
+  </si>
+  <si>
+    <t>minh123</t>
+  </si>
+  <si>
+    <t>Minh@123</t>
+  </si>
+  <si>
+    <t>minh1234</t>
+  </si>
+  <si>
+    <t>Minh@1234</t>
+  </si>
+  <si>
+    <t>minh12345</t>
+  </si>
+  <si>
+    <t>Minh@12345</t>
+  </si>
+  <si>
+    <t>35 Miếu Đầm, Hà Nội</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Thông</t>
+  </si>
+  <si>
+    <t>0862452677</t>
+  </si>
+  <si>
+    <t>nguyenxuanthong_UID09@gmail.com</t>
+  </si>
+  <si>
+    <t>SID0006</t>
+  </si>
+  <si>
+    <t>SID0001</t>
+  </si>
+  <si>
+    <t>SID0002</t>
+  </si>
+  <si>
+    <t>SID0003</t>
+  </si>
+  <si>
+    <t>SID0004</t>
+  </si>
+  <si>
+    <t>SID0005</t>
+  </si>
+  <si>
+    <t>CID0006</t>
+  </si>
+  <si>
+    <t>CID0001</t>
+  </si>
+  <si>
+    <t>CID0002</t>
+  </si>
+  <si>
+    <t>CID0003</t>
+  </si>
+  <si>
+    <t>CID0004</t>
+  </si>
+  <si>
+    <t>CID0005</t>
+  </si>
+  <si>
+    <t>AID0003</t>
+  </si>
+  <si>
+    <t>AID0001</t>
+  </si>
+  <si>
+    <t>AID0002</t>
+  </si>
+  <si>
+    <t>BiID0001</t>
+  </si>
+  <si>
+    <t>BiID0002</t>
+  </si>
+  <si>
+    <t>BiID0003</t>
+  </si>
+  <si>
+    <t>BiID0004</t>
+  </si>
+  <si>
+    <t>BiID0005</t>
+  </si>
+  <si>
+    <t>BiID0006</t>
+  </si>
+  <si>
+    <t>BiID0007</t>
+  </si>
+  <si>
+    <t>BiID0008</t>
+  </si>
+  <si>
+    <t>BiID0009</t>
+  </si>
+  <si>
+    <t>BiID0010</t>
+  </si>
+  <si>
+    <t>BiID0011</t>
+  </si>
+  <si>
+    <t>BiID0012</t>
+  </si>
+  <si>
+    <t>BiID0013</t>
+  </si>
+  <si>
+    <t>BiID0014</t>
+  </si>
+  <si>
+    <t>BiID0015</t>
+  </si>
+  <si>
+    <t>BiID0016</t>
+  </si>
+  <si>
+    <t>BiID0017</t>
+  </si>
+  <si>
+    <t>BiID0018</t>
+  </si>
+  <si>
+    <t>BiID0019</t>
+  </si>
+  <si>
+    <t>BiID0020</t>
+  </si>
+  <si>
+    <t>BiID0021</t>
+  </si>
+  <si>
+    <t>BiID0022</t>
+  </si>
+  <si>
+    <t>BiID0023</t>
+  </si>
+  <si>
+    <t>BiID0024</t>
+  </si>
+  <si>
+    <t>BiID0025</t>
+  </si>
+  <si>
+    <t>BiID0026</t>
+  </si>
+  <si>
+    <t>BiID0027</t>
+  </si>
+  <si>
+    <t>BiID0028</t>
+  </si>
+  <si>
+    <t>BiID0029</t>
+  </si>
+  <si>
+    <t>BiID0030</t>
+  </si>
+  <si>
+    <t>BiID0031</t>
+  </si>
+  <si>
+    <t>BiID0032</t>
+  </si>
+  <si>
+    <t>BiID0033</t>
+  </si>
+  <si>
+    <t>BiID0034</t>
+  </si>
+  <si>
+    <t>BiID0035</t>
+  </si>
+  <si>
+    <t>BiID0036</t>
+  </si>
+  <si>
+    <t>BiID0037</t>
+  </si>
+  <si>
+    <t>BiID0038</t>
+  </si>
+  <si>
+    <t>BiID0039</t>
+  </si>
+  <si>
+    <t>BiID0040</t>
+  </si>
+  <si>
+    <t>BID0041</t>
+  </si>
+  <si>
+    <t>BID0069</t>
+  </si>
+  <si>
+    <t>BID0020</t>
+  </si>
+  <si>
+    <t>BID0051</t>
+  </si>
+  <si>
+    <t>BID0072</t>
+  </si>
+  <si>
+    <t>BID0039</t>
+  </si>
+  <si>
+    <t>BID0028</t>
+  </si>
+  <si>
+    <t>BID0067</t>
+  </si>
+  <si>
+    <t>BID0005</t>
+  </si>
+  <si>
+    <t>BID0034</t>
+  </si>
+  <si>
+    <t>BID0024</t>
+  </si>
+  <si>
+    <t>BID0031</t>
+  </si>
+  <si>
+    <t>BID0019</t>
+  </si>
+  <si>
+    <t>BID0058</t>
+  </si>
+  <si>
+    <t>BID0036</t>
+  </si>
+  <si>
+    <t>BID0071</t>
+  </si>
+  <si>
+    <t>BID0077</t>
+  </si>
+  <si>
+    <t>BID0048</t>
+  </si>
+  <si>
+    <t>BID0074</t>
+  </si>
+  <si>
+    <t>BID0043</t>
+  </si>
+  <si>
+    <t>BID0022</t>
+  </si>
+  <si>
+    <t>BID0011</t>
+  </si>
+  <si>
+    <t>BID0044</t>
+  </si>
+  <si>
+    <t>BID0010</t>
+  </si>
+  <si>
+    <t>BID0017</t>
+  </si>
+  <si>
+    <t>BID0060</t>
+  </si>
+  <si>
+    <t>BID0032</t>
+  </si>
+  <si>
+    <t>BID0007</t>
+  </si>
+  <si>
+    <t>BID0029</t>
+  </si>
+  <si>
+    <t>BID0027</t>
+  </si>
+  <si>
+    <t>BID0035</t>
+  </si>
+  <si>
+    <t>BID0008</t>
+  </si>
+  <si>
+    <t>BID0033</t>
+  </si>
+  <si>
+    <t>BID0003</t>
+  </si>
+  <si>
+    <t>BID0061</t>
+  </si>
+  <si>
+    <t>BID0026</t>
+  </si>
+  <si>
+    <t>BID0015</t>
+  </si>
+  <si>
+    <t>BID0054</t>
+  </si>
+  <si>
+    <t>BID0079</t>
+  </si>
+  <si>
+    <t>BID0050</t>
+  </si>
+  <si>
+    <t>BID0053</t>
+  </si>
+  <si>
+    <t>BID0009</t>
+  </si>
+  <si>
+    <t>BID0001</t>
+  </si>
+  <si>
+    <t>BID0076</t>
+  </si>
+  <si>
+    <t>BID0078</t>
+  </si>
+  <si>
+    <t>BID0040</t>
+  </si>
+  <si>
+    <t>BID0065</t>
+  </si>
+  <si>
+    <t>BID0052</t>
+  </si>
+  <si>
+    <t>BID0066</t>
+  </si>
+  <si>
+    <t>AuID0001</t>
+  </si>
+  <si>
+    <t>AuID0002</t>
+  </si>
+  <si>
+    <t>AuID0003</t>
+  </si>
+  <si>
+    <t>AuID0004</t>
+  </si>
+  <si>
+    <t>AuID0005</t>
+  </si>
+  <si>
+    <t>AuID0006</t>
+  </si>
+  <si>
+    <t>AuID0007</t>
+  </si>
+  <si>
+    <t>AuID0008</t>
+  </si>
+  <si>
+    <t>AuID0009</t>
+  </si>
+  <si>
+    <t>AuID0010</t>
+  </si>
+  <si>
+    <t>AuID0011</t>
+  </si>
+  <si>
+    <t>AuID0012</t>
+  </si>
+  <si>
+    <t>AuID0013</t>
+  </si>
+  <si>
+    <t>AuID0014</t>
+  </si>
+  <si>
+    <t>AuID0015</t>
+  </si>
+  <si>
+    <t>AuID0017</t>
+  </si>
+  <si>
+    <t>AuID0018</t>
+  </si>
+  <si>
+    <t>AuID0019</t>
+  </si>
+  <si>
+    <t>AuID0020</t>
+  </si>
+  <si>
+    <t>AuID0021</t>
+  </si>
+  <si>
+    <t>AuID0022</t>
+  </si>
+  <si>
+    <t>PID0001</t>
+  </si>
+  <si>
+    <t>PID0002</t>
+  </si>
+  <si>
+    <t>PID0003</t>
+  </si>
+  <si>
+    <t>PID0004</t>
+  </si>
+  <si>
+    <t>PID0005</t>
+  </si>
+  <si>
+    <t>PID0006</t>
+  </si>
+  <si>
+    <t>PID0007</t>
+  </si>
+  <si>
+    <t>PID0008</t>
+  </si>
+  <si>
+    <t>PID0009</t>
+  </si>
+  <si>
+    <t>PID0010</t>
+  </si>
+  <si>
+    <t>PID0011</t>
+  </si>
+  <si>
+    <t>PID0012</t>
+  </si>
+  <si>
+    <t>PID0013</t>
+  </si>
+  <si>
+    <t>PID0014</t>
+  </si>
+  <si>
+    <t>BID0002</t>
+  </si>
+  <si>
+    <t>BID0004</t>
+  </si>
+  <si>
+    <t>BID0006</t>
+  </si>
+  <si>
+    <t>BID0012</t>
+  </si>
+  <si>
+    <t>BID0013</t>
+  </si>
+  <si>
+    <t>BID0014</t>
+  </si>
+  <si>
+    <t>BID0016</t>
+  </si>
+  <si>
+    <t>BID0018</t>
+  </si>
+  <si>
+    <t>BID0021</t>
+  </si>
+  <si>
+    <t>BID0023</t>
+  </si>
+  <si>
+    <t>BID0025</t>
+  </si>
+  <si>
+    <t>BID0030</t>
+  </si>
+  <si>
+    <t>BID0037</t>
+  </si>
+  <si>
+    <t>BID0038</t>
+  </si>
+  <si>
+    <t>BID0042</t>
+  </si>
+  <si>
+    <t>BID0045</t>
+  </si>
+  <si>
+    <t>BID0046</t>
+  </si>
+  <si>
+    <t>BID0047</t>
+  </si>
+  <si>
+    <t>BID0049</t>
+  </si>
+  <si>
+    <t>BID0055</t>
+  </si>
+  <si>
+    <t>BID0056</t>
+  </si>
+  <si>
+    <t>BID0057</t>
+  </si>
+  <si>
+    <t>BID0059</t>
+  </si>
+  <si>
+    <t>BID0062</t>
+  </si>
+  <si>
+    <t>BID0063</t>
+  </si>
+  <si>
+    <t>BID0064</t>
+  </si>
+  <si>
+    <t>BID0068</t>
+  </si>
+  <si>
+    <t>BID0070</t>
+  </si>
+  <si>
+    <t>BID0073</t>
+  </si>
+  <si>
+    <t>BID0075</t>
+  </si>
+  <si>
+    <t>BID0080</t>
+  </si>
+  <si>
+    <t>BID0081</t>
+  </si>
+  <si>
+    <t>BID0082</t>
+  </si>
+  <si>
+    <t>BID0083</t>
+  </si>
+  <si>
+    <t>BID0084</t>
+  </si>
+  <si>
+    <t>BID0085</t>
+  </si>
+  <si>
+    <t>BID0086</t>
+  </si>
+  <si>
+    <t>AuID0016</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1796,7 +1860,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1825,6 +1889,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2068,8 +2133,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1002"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H1005"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -2110,344 +2175,419 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="22" t="s">
+        <v>282</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="10" t="str">
-        <f>A2&amp;D2</f>
-        <v>SID01staff</v>
-      </c>
-      <c r="C2" s="23" t="str">
-        <f>A2&amp;"@"&amp;D2</f>
-        <v>SID01@staff</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>265</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>355</v>
+        <v>266</v>
       </c>
       <c r="G2" t="s">
-        <v>5</v>
+        <v>264</v>
       </c>
       <c r="H2" t="s">
-        <v>365</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>30</v>
+        <v>283</v>
       </c>
       <c r="B3" s="10" t="str">
-        <f t="shared" ref="B3:B13" si="0">A3&amp;D3</f>
-        <v>SID02staff</v>
+        <f>A3&amp;D3</f>
+        <v>SID0001staff</v>
       </c>
       <c r="C3" s="23" t="str">
-        <f t="shared" ref="C3:C13" si="1">A3&amp;"@"&amp;D3</f>
-        <v>SID02@staff</v>
+        <f>A3&amp;"@"&amp;D3</f>
+        <v>SID0001@staff</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>356</v>
+        <v>183</v>
       </c>
       <c r="G3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>366</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>31</v>
+        <v>284</v>
       </c>
       <c r="B4" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>SID03staff</v>
+        <f t="shared" ref="B4:B16" si="0">A4&amp;D4</f>
+        <v>SID0002staff</v>
       </c>
       <c r="C4" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>SID03@staff</v>
+        <f t="shared" ref="C4:C16" si="1">A4&amp;"@"&amp;D4</f>
+        <v>SID0002@staff</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="18" t="s">
-        <v>419</v>
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>6</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>421</v>
+        <v>184</v>
       </c>
       <c r="G4" t="s">
-        <v>423</v>
-      </c>
-      <c r="H4" s="14" t="s">
-        <v>425</v>
+        <v>7</v>
+      </c>
+      <c r="H4" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>417</v>
+        <v>285</v>
       </c>
       <c r="B5" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>SID04staff</v>
+        <v>SID0003staff</v>
       </c>
       <c r="C5" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>SID04@staff</v>
+        <v>SID0003@staff</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>420</v>
+        <v>245</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>422</v>
+        <v>247</v>
       </c>
       <c r="G5" t="s">
-        <v>424</v>
+        <v>249</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>426</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>418</v>
+        <v>286</v>
       </c>
       <c r="B6" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>SID05staff</v>
+        <v>SID0004staff</v>
       </c>
       <c r="C6" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>SID05@staff</v>
+        <v>SID0004@staff</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
+        <v>28</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>246</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>357</v>
+        <v>248</v>
       </c>
       <c r="G6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" t="s">
-        <v>367</v>
+        <v>250</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>32</v>
+        <v>287</v>
       </c>
       <c r="B7" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>CID01client</v>
+        <v>SID0005staff</v>
       </c>
       <c r="C7" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>CID01@client</v>
+        <v>SID0005@staff</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>358</v>
+        <v>185</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>368</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="10" t="str">
-        <f t="shared" si="0"/>
-        <v>CID02client</v>
-      </c>
-      <c r="C8" s="23" t="str">
-        <f t="shared" si="1"/>
-        <v>CID02@client</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>359</v>
+      <c r="A8" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>270</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="H8" t="s">
-        <v>369</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>35</v>
+        <v>289</v>
       </c>
       <c r="B9" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>CID03client</v>
+        <v>CID0001client</v>
       </c>
       <c r="C9" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>CID03@client</v>
+        <v>CID0001@client</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>360</v>
+        <v>186</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>370</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>36</v>
+        <v>290</v>
       </c>
       <c r="B10" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>CID04client</v>
+        <v>CID0002client</v>
       </c>
       <c r="C10" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>CID04@client</v>
+        <v>CID0002@client</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>361</v>
+        <v>187</v>
       </c>
       <c r="G10" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>371</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>37</v>
+        <v>291</v>
       </c>
       <c r="B11" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>CID05client</v>
+        <v>CID0003client</v>
       </c>
       <c r="C11" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>CID05@client</v>
+        <v>CID0003@client</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>362</v>
+        <v>188</v>
       </c>
       <c r="G11" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>372</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>38</v>
+        <v>292</v>
       </c>
       <c r="B12" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>AID01admin</v>
+        <v>CID0004client</v>
       </c>
       <c r="C12" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>AID01@admin</v>
+        <v>CID0004@client</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>363</v>
+        <v>189</v>
       </c>
       <c r="G12" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>373</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>40</v>
+        <v>293</v>
       </c>
       <c r="B13" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>AID02admin</v>
+        <v>CID0005client</v>
       </c>
       <c r="C13" s="23" t="str">
         <f t="shared" si="1"/>
-        <v>AID02@admin</v>
+        <v>CID0005@client</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="G14" t="s">
+        <v>278</v>
+      </c>
+      <c r="H14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="B15" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>AID0001admin</v>
+      </c>
+      <c r="C15" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>AID0001@admin</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G15" t="s">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B16" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>AID0002admin</v>
+      </c>
+      <c r="C16" s="23" t="str">
+        <f t="shared" si="1"/>
+        <v>AID0002@admin</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="G13" t="s">
+      <c r="F16" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="G16" t="s">
         <v>23</v>
       </c>
-      <c r="H13" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="H16" t="s">
+        <v>202</v>
+      </c>
+    </row>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3434,11 +3574,14 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="H4" r:id="rId1"/>
-    <hyperlink ref="H5" r:id="rId2"/>
+    <hyperlink ref="H5" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="H6" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId3"/>
@@ -3447,7 +3590,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3457,27 +3600,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>427</v>
+        <v>253</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>428</v>
+        <v>254</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>429</v>
+        <v>255</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="B2">
         <v>7360000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>432</v>
+        <v>258</v>
       </c>
       <c r="D2" s="19">
         <v>45174</v>
@@ -3486,13 +3629,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>284</v>
       </c>
       <c r="B3">
         <v>6430000</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>431</v>
+        <v>257</v>
       </c>
       <c r="D3" s="19">
         <v>45107</v>
@@ -3501,13 +3644,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>31</v>
+        <v>285</v>
       </c>
       <c r="B4">
         <v>4780000</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>430</v>
+        <v>256</v>
       </c>
       <c r="D4" s="20">
         <v>45091</v>
@@ -3516,13 +3659,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>417</v>
+        <v>286</v>
       </c>
       <c r="B5">
         <v>4540000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>430</v>
+        <v>256</v>
       </c>
       <c r="D5" s="19">
         <v>44955</v>
@@ -3531,13 +3674,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>418</v>
+        <v>287</v>
       </c>
       <c r="B6">
         <v>7160000</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>432</v>
+        <v>258</v>
       </c>
       <c r="D6" s="19">
         <v>45048</v>
@@ -3546,13 +3689,13 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>38</v>
+        <v>295</v>
       </c>
       <c r="B7">
         <v>7160000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D7" s="19">
         <v>44954</v>
@@ -3561,13 +3704,13 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>40</v>
+        <v>296</v>
       </c>
       <c r="B8">
         <v>7160000</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D8" s="19">
         <v>44932</v>
@@ -3580,7 +3723,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -3592,576 +3735,576 @@
   <sheetData>
     <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D1" s="22" t="s">
-        <v>434</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C2" s="2">
         <v>44885</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2">
         <v>44886</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2">
         <v>44887</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>300</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C5" s="2">
         <v>44888</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C6" s="2">
         <v>44889</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>302</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C7" s="2">
         <v>44890</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>303</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C8" s="2">
         <v>44891</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="C9" s="2">
         <v>44892</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C10" s="2">
         <v>44893</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>306</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C11" s="2">
         <v>44894</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C12" s="2">
         <v>44895</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C13" s="2">
         <v>44896</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C14" s="2">
         <v>44897</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C15" s="2">
         <v>44898</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C16" s="2">
         <v>44899</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>312</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C17" s="2">
         <v>44900</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>313</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C18" s="2">
         <v>44901</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C19" s="2">
         <v>44902</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>315</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C20" s="2">
         <v>44903</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C21" s="2">
         <v>44904</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C22" s="2">
         <v>44905</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C23" s="2">
         <v>44906</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>319</v>
       </c>
       <c r="B24" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="C24" s="2">
         <v>44907</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C25" s="2">
         <v>44908</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C26" s="2">
         <v>44909</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>322</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2">
         <v>44910</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C28" s="2">
         <v>44911</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>324</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C29" s="2">
         <v>44912</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="B30" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C30" s="2">
         <v>44913</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>326</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C31" s="2">
         <v>44914</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="B32" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2">
         <v>44915</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>32</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2">
         <v>44916</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2">
         <v>44917</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>290</v>
       </c>
       <c r="C35" s="2">
         <v>44918</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2">
         <v>44919</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>291</v>
       </c>
       <c r="C37" s="2">
         <v>44920</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C38" s="2">
         <v>44921</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>293</v>
       </c>
       <c r="C39" s="2">
         <v>44922</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>435</v>
+        <v>261</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C40" s="2">
         <v>44923</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>437</v>
+        <v>263</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>292</v>
       </c>
       <c r="C41" s="2">
         <v>44924</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>436</v>
+        <v>262</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -5173,6 +5316,7 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -5180,7 +5324,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C1006"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -5192,21 +5336,21 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>353</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="B2" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="C2" s="1">
         <v>8</v>
@@ -5214,10 +5358,10 @@
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="B3" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C3" s="1">
         <v>6</v>
@@ -5226,10 +5370,10 @@
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="str">
         <f>A3</f>
-        <v>BiID02</v>
+        <v>BiID0002</v>
       </c>
       <c r="B4" t="s">
-        <v>219</v>
+        <v>339</v>
       </c>
       <c r="C4" s="1">
         <v>2</v>
@@ -5237,10 +5381,10 @@
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="B5" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="C5" s="1">
         <v>2</v>
@@ -5248,10 +5392,10 @@
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>44</v>
+        <v>298</v>
       </c>
       <c r="B6" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C6" s="1">
         <v>9</v>
@@ -5259,10 +5403,10 @@
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="B7" t="s">
-        <v>257</v>
+        <v>342</v>
       </c>
       <c r="C7" s="1">
         <v>6</v>
@@ -5270,10 +5414,10 @@
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>45</v>
+        <v>299</v>
       </c>
       <c r="B8" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="C8" s="1">
         <v>8</v>
@@ -5282,10 +5426,10 @@
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="str">
         <f>A8</f>
-        <v>BiID03</v>
+        <v>BiID0003</v>
       </c>
       <c r="B9" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="C9" s="1">
         <v>4</v>
@@ -5293,10 +5437,10 @@
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>300</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>345</v>
       </c>
       <c r="C10" s="1">
         <v>8</v>
@@ -5304,10 +5448,10 @@
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="B11" t="s">
-        <v>247</v>
+        <v>346</v>
       </c>
       <c r="C11" s="1">
         <v>5</v>
@@ -5315,10 +5459,10 @@
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="B12" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -5326,10 +5470,10 @@
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>47</v>
+        <v>301</v>
       </c>
       <c r="B13" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
       <c r="C13" s="1">
         <v>5</v>
@@ -5338,10 +5482,10 @@
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="str">
         <f>A12</f>
-        <v>BiID05</v>
+        <v>BiID0005</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>349</v>
       </c>
       <c r="C14" s="1">
         <v>4</v>
@@ -5349,10 +5493,10 @@
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>48</v>
+        <v>302</v>
       </c>
       <c r="B15" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="C15" s="1">
         <v>4</v>
@@ -5360,10 +5504,10 @@
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>49</v>
+        <v>303</v>
       </c>
       <c r="B16" t="s">
-        <v>251</v>
+        <v>351</v>
       </c>
       <c r="C16" s="1">
         <v>2</v>
@@ -5371,10 +5515,10 @@
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>49</v>
+        <v>303</v>
       </c>
       <c r="B17" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
@@ -5382,10 +5526,10 @@
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>50</v>
+        <v>304</v>
       </c>
       <c r="B18" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="C18" s="1">
         <v>5</v>
@@ -5393,10 +5537,10 @@
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="B19" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C19" s="1">
         <v>8</v>
@@ -5404,10 +5548,10 @@
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="B20" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
@@ -5415,10 +5559,10 @@
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>51</v>
+        <v>305</v>
       </c>
       <c r="B21" t="s">
-        <v>257</v>
+        <v>342</v>
       </c>
       <c r="C21" s="1">
         <v>9</v>
@@ -5426,10 +5570,10 @@
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>52</v>
+        <v>306</v>
       </c>
       <c r="B22" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="C22" s="1">
         <v>5</v>
@@ -5437,10 +5581,10 @@
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B23" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="C23" s="1">
         <v>10</v>
@@ -5448,10 +5592,10 @@
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B24" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="C24" s="1">
         <v>5</v>
@@ -5459,10 +5603,10 @@
     </row>
     <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>53</v>
+        <v>307</v>
       </c>
       <c r="B25" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
       <c r="C25" s="1">
         <v>8</v>
@@ -5470,10 +5614,10 @@
     </row>
     <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="B26" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="C26" s="1">
         <v>4</v>
@@ -5481,10 +5625,10 @@
     </row>
     <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="B27" t="s">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="C27" s="1">
         <v>10</v>
@@ -5492,10 +5636,10 @@
     </row>
     <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="C28" s="1">
         <v>4</v>
@@ -5503,10 +5647,10 @@
     </row>
     <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>55</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="C29" s="1">
         <v>3</v>
@@ -5514,10 +5658,10 @@
     </row>
     <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="C30" s="1">
         <v>6</v>
@@ -5525,10 +5669,10 @@
     </row>
     <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>56</v>
+        <v>310</v>
       </c>
       <c r="B31" t="s">
-        <v>213</v>
+        <v>361</v>
       </c>
       <c r="C31" s="1">
         <v>9</v>
@@ -5536,10 +5680,10 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
-        <v>57</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C32" s="1">
         <v>2</v>
@@ -5547,10 +5691,10 @@
     </row>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
-        <v>58</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="C33" s="1">
         <v>2</v>
@@ -5558,10 +5702,10 @@
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
-        <v>59</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="C34" s="1">
         <v>3</v>
@@ -5569,10 +5713,10 @@
     </row>
     <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="4" t="s">
-        <v>59</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s">
-        <v>193</v>
+        <v>364</v>
       </c>
       <c r="C35" s="1">
         <v>10</v>
@@ -5580,10 +5724,10 @@
     </row>
     <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
-        <v>60</v>
+        <v>314</v>
       </c>
       <c r="B36" t="s">
-        <v>237</v>
+        <v>365</v>
       </c>
       <c r="C36" s="1">
         <v>7</v>
@@ -5591,10 +5735,10 @@
     </row>
     <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
-        <v>61</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="C37" s="1">
         <v>2</v>
@@ -5602,10 +5746,10 @@
     </row>
     <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B38" t="s">
-        <v>249</v>
+        <v>367</v>
       </c>
       <c r="C38" s="1">
         <v>4</v>
@@ -5613,10 +5757,10 @@
     </row>
     <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="C39" s="1">
         <v>2</v>
@@ -5624,10 +5768,10 @@
     </row>
     <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B40" t="s">
-        <v>245</v>
+        <v>369</v>
       </c>
       <c r="C40" s="1">
         <v>6</v>
@@ -5635,10 +5779,10 @@
     </row>
     <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4" t="s">
-        <v>62</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="C41" s="1">
         <v>1</v>
@@ -5646,10 +5790,10 @@
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="C42" s="1">
         <v>9</v>
@@ -5657,10 +5801,10 @@
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
-        <v>63</v>
+        <v>317</v>
       </c>
       <c r="B43" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="C43" s="1">
         <v>10</v>
@@ -5668,10 +5812,10 @@
     </row>
     <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
-        <v>64</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s">
-        <v>209</v>
+        <v>373</v>
       </c>
       <c r="C44" s="1">
         <v>6</v>
@@ -5679,10 +5823,10 @@
     </row>
     <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4" t="s">
-        <v>65</v>
+        <v>319</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>361</v>
       </c>
       <c r="C45" s="1">
         <v>7</v>
@@ -5690,10 +5834,10 @@
     </row>
     <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
-        <v>65</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s">
-        <v>287</v>
+        <v>374</v>
       </c>
       <c r="C46" s="1">
         <v>8</v>
@@ -5701,10 +5845,10 @@
     </row>
     <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="B47" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="C47" s="1">
         <v>7</v>
@@ -5712,10 +5856,10 @@
     </row>
     <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
-        <v>66</v>
+        <v>320</v>
       </c>
       <c r="B48" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="C48" s="1">
         <v>10</v>
@@ -5723,10 +5867,10 @@
     </row>
     <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4" t="s">
-        <v>67</v>
+        <v>321</v>
       </c>
       <c r="B49" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="C49" s="1">
         <v>6</v>
@@ -5734,10 +5878,10 @@
     </row>
     <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
-        <v>68</v>
+        <v>322</v>
       </c>
       <c r="B50" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="C50" s="1">
         <v>1</v>
@@ -5745,10 +5889,10 @@
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B51" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="C51" s="1">
         <v>3</v>
@@ -5756,10 +5900,10 @@
     </row>
     <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="C52" s="1">
         <v>5</v>
@@ -5767,10 +5911,10 @@
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4" t="s">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B53" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="C53" s="1">
         <v>3</v>
@@ -5778,10 +5922,10 @@
     </row>
     <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4" t="s">
-        <v>69</v>
+        <v>323</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>378</v>
       </c>
       <c r="C54" s="1">
         <v>6</v>
@@ -5789,10 +5933,10 @@
     </row>
     <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4" t="s">
-        <v>70</v>
+        <v>324</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>181</v>
+        <v>379</v>
       </c>
       <c r="C55" s="1">
         <v>7</v>
@@ -5800,10 +5944,10 @@
     </row>
     <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="C56" s="1">
         <v>2</v>
@@ -5811,10 +5955,10 @@
     </row>
     <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="C57" s="1">
         <v>9</v>
@@ -5822,10 +5966,10 @@
     </row>
     <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4" t="s">
-        <v>72</v>
+        <v>326</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="C58" s="1">
         <v>6</v>
@@ -5833,10 +5977,10 @@
     </row>
     <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4" t="s">
-        <v>72</v>
+        <v>326</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="C59" s="1">
         <v>1</v>
@@ -5844,10 +5988,10 @@
     </row>
     <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4" t="s">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="C60" s="1">
         <v>8</v>
@@ -5855,10 +5999,10 @@
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4" t="s">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C61" s="1">
         <v>9</v>
@@ -5866,10 +6010,10 @@
     </row>
     <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4" t="s">
-        <v>74</v>
+        <v>328</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="C62" s="1">
         <v>6</v>
@@ -5877,10 +6021,10 @@
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="C63" s="1">
         <v>2</v>
@@ -5888,10 +6032,10 @@
     </row>
     <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="C64" s="1">
         <v>10</v>
@@ -5899,10 +6043,10 @@
     </row>
     <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4" t="s">
-        <v>75</v>
+        <v>329</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="C65" s="1">
         <v>10</v>
@@ -5910,10 +6054,10 @@
     </row>
     <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4" t="s">
-        <v>76</v>
+        <v>330</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="C66" s="1">
         <v>2</v>
@@ -5921,10 +6065,10 @@
     </row>
     <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4" t="s">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="C67" s="1">
         <v>9</v>
@@ -5932,10 +6076,10 @@
     </row>
     <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4" t="s">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="C68" s="1">
         <v>10</v>
@@ -5943,10 +6087,10 @@
     </row>
     <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4" t="s">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="C69" s="1">
         <v>4</v>
@@ -5954,10 +6098,10 @@
     </row>
     <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4" t="s">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="C70" s="1">
         <v>5</v>
@@ -5965,10 +6109,10 @@
     </row>
     <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>332</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="C71" s="1">
         <v>6</v>
@@ -5976,10 +6120,10 @@
     </row>
     <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4" t="s">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="C72" s="1">
         <v>4</v>
@@ -5987,10 +6131,10 @@
     </row>
     <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="C73" s="1">
         <v>4</v>
@@ -5998,10 +6142,10 @@
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="C74" s="1">
         <v>4</v>
@@ -6009,10 +6153,10 @@
     </row>
     <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4" t="s">
-        <v>80</v>
+        <v>334</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C75" s="1">
         <v>4</v>
@@ -6021,10 +6165,10 @@
     <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4" t="str">
         <f>A77</f>
-        <v>BiID39</v>
+        <v>BiID0039</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="C76" s="1">
         <v>2</v>
@@ -6032,10 +6176,10 @@
     </row>
     <row r="77" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4" t="s">
-        <v>81</v>
+        <v>335</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>249</v>
+        <v>367</v>
       </c>
       <c r="C77" s="1">
         <v>9</v>
@@ -6043,10 +6187,10 @@
     </row>
     <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="C78" s="1">
         <v>3</v>
@@ -6054,10 +6198,10 @@
     </row>
     <row r="79" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>209</v>
+        <v>373</v>
       </c>
       <c r="C79" s="1">
         <v>9</v>
@@ -6065,10 +6209,10 @@
     </row>
     <row r="80" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4" t="s">
-        <v>82</v>
+        <v>336</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="C80" s="1">
         <v>10</v>
@@ -7122,7 +7266,7 @@
     <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <sortState ref="A2:A80">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A80">
     <sortCondition ref="A2:A80"/>
   </sortState>
   <phoneticPr fontId="14" type="noConversion"/>
@@ -7133,7 +7277,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -7145,255 +7289,255 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>375</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>387</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>35</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>376</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>388</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>36</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>377</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>90</v>
+        <v>389</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>378</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>92</v>
+        <v>390</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>379</v>
+        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>94</v>
+        <v>391</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>39</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>380</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>96</v>
+        <v>392</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>381</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>98</v>
+        <v>393</v>
       </c>
       <c r="B9" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>382</v>
+        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>383</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>102</v>
+        <v>395</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>43</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>384</v>
+        <v>212</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>104</v>
+        <v>396</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>44</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>385</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>106</v>
+        <v>397</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>45</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>386</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="B14" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>387</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>110</v>
+        <v>399</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>388</v>
+        <v>216</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>48</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>389</v>
+        <v>217</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>114</v>
+      <c r="A17" s="1" t="s">
+        <v>458</v>
       </c>
       <c r="B17" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>390</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>116</v>
+      <c r="A18" s="1" t="s">
+        <v>401</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>391</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>118</v>
+      <c r="A19" s="1" t="s">
+        <v>402</v>
       </c>
       <c r="B19" t="s">
-        <v>119</v>
+        <v>51</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>392</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>120</v>
+      <c r="A20" s="1" t="s">
+        <v>403</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>393</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>122</v>
+      <c r="A21" s="1" t="s">
+        <v>404</v>
       </c>
       <c r="B21" t="s">
-        <v>123</v>
+        <v>53</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>394</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>124</v>
+      <c r="A22" s="1" t="s">
+        <v>405</v>
       </c>
       <c r="B22" t="s">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>395</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>126</v>
+      <c r="A23" s="1" t="s">
+        <v>406</v>
       </c>
       <c r="B23" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>396</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8374,6 +8518,7 @@
     <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
@@ -8381,7 +8526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -8393,167 +8538,167 @@
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>135</v>
+        <v>63</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>141</v>
+        <v>67</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>142</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>144</v>
+        <v>69</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>145</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>71</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>148</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>75</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>413</v>
       </c>
       <c r="B8" t="s">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>157</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>158</v>
+        <v>414</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>79</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>160</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>161</v>
+        <v>415</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>81</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>164</v>
+        <v>416</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>165</v>
+        <v>83</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>166</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>167</v>
+        <v>417</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>169</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>418</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>172</v>
+        <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>173</v>
+        <v>419</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>176</v>
+        <v>420</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>91</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>178</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11513,19 +11658,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1"/>
-    <hyperlink ref="C4" r:id="rId2"/>
-    <hyperlink ref="C5" r:id="rId3"/>
-    <hyperlink ref="C6" r:id="rId4"/>
-    <hyperlink ref="C7" r:id="rId5"/>
-    <hyperlink ref="C8" r:id="rId6"/>
-    <hyperlink ref="C9" r:id="rId7"/>
-    <hyperlink ref="C10" r:id="rId8"/>
-    <hyperlink ref="C11" r:id="rId9"/>
-    <hyperlink ref="C12" r:id="rId10"/>
-    <hyperlink ref="C13" r:id="rId11"/>
-    <hyperlink ref="C14" r:id="rId12"/>
-    <hyperlink ref="C15" r:id="rId13"/>
+    <hyperlink ref="C3" r:id="rId1" xr:uid="{00000000-0004-0000-0500-000000000000}"/>
+    <hyperlink ref="C4" r:id="rId2" xr:uid="{00000000-0004-0000-0500-000001000000}"/>
+    <hyperlink ref="C5" r:id="rId3" xr:uid="{00000000-0004-0000-0500-000002000000}"/>
+    <hyperlink ref="C6" r:id="rId4" xr:uid="{00000000-0004-0000-0500-000003000000}"/>
+    <hyperlink ref="C7" r:id="rId5" xr:uid="{00000000-0004-0000-0500-000004000000}"/>
+    <hyperlink ref="C8" r:id="rId6" xr:uid="{00000000-0004-0000-0500-000005000000}"/>
+    <hyperlink ref="C9" r:id="rId7" xr:uid="{00000000-0004-0000-0500-000006000000}"/>
+    <hyperlink ref="C10" r:id="rId8" xr:uid="{00000000-0004-0000-0500-000007000000}"/>
+    <hyperlink ref="C11" r:id="rId9" xr:uid="{00000000-0004-0000-0500-000008000000}"/>
+    <hyperlink ref="C12" r:id="rId10" xr:uid="{00000000-0004-0000-0500-000009000000}"/>
+    <hyperlink ref="C13" r:id="rId11" xr:uid="{00000000-0004-0000-0500-00000A000000}"/>
+    <hyperlink ref="C14" r:id="rId12" xr:uid="{00000000-0004-0000-0500-00000B000000}"/>
+    <hyperlink ref="C15" r:id="rId13" xr:uid="{00000000-0004-0000-0500-00000C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
@@ -11533,7 +11678,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:G1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
@@ -11547,42 +11692,42 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>179</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>180</v>
+        <v>94</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>433</v>
+        <v>259</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>353</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>354</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>181</v>
+        <v>379</v>
       </c>
       <c r="B2" t="s">
-        <v>182</v>
+        <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>84</v>
+        <v>386</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>408</v>
+        <v>236</v>
       </c>
       <c r="F2" s="1">
         <v>15</v>
@@ -11593,19 +11738,19 @@
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>183</v>
+        <v>421</v>
       </c>
       <c r="B3" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>86</v>
+        <v>387</v>
       </c>
       <c r="D3" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="F3" s="1">
         <v>58</v>
@@ -11616,19 +11761,19 @@
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>185</v>
+        <v>370</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>186</v>
+        <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>88</v>
+        <v>388</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>398</v>
+        <v>226</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -11639,19 +11784,19 @@
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>187</v>
+        <v>422</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>188</v>
+        <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>90</v>
+        <v>389</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>397</v>
+        <v>225</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -11662,19 +11807,19 @@
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>189</v>
+        <v>345</v>
       </c>
       <c r="B6" t="s">
-        <v>190</v>
+        <v>99</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>92</v>
+        <v>390</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>410</v>
+        <v>238</v>
       </c>
       <c r="F6">
         <v>36</v>
@@ -11685,19 +11830,19 @@
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>191</v>
+        <v>423</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>192</v>
+        <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>94</v>
+        <v>391</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>401</v>
+        <v>229</v>
       </c>
       <c r="F7">
         <v>68</v>
@@ -11708,19 +11853,19 @@
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>193</v>
+        <v>364</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>194</v>
+        <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>96</v>
+        <v>392</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>140</v>
+        <v>408</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>411</v>
+        <v>239</v>
       </c>
       <c r="F8">
         <v>79</v>
@@ -11731,19 +11876,19 @@
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>195</v>
+        <v>368</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>98</v>
+        <v>393</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>400</v>
+        <v>228</v>
       </c>
       <c r="F9">
         <v>82</v>
@@ -11754,19 +11899,19 @@
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>197</v>
+        <v>378</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>100</v>
+        <v>394</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>402</v>
+        <v>230</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -11777,19 +11922,19 @@
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>199</v>
+        <v>360</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>102</v>
+        <v>395</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="F11">
         <v>24</v>
@@ -11800,19 +11945,19 @@
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>201</v>
+        <v>358</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>202</v>
+        <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>104</v>
+        <v>396</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>403</v>
+        <v>231</v>
       </c>
       <c r="F12">
         <v>28</v>
@@ -11823,19 +11968,19 @@
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>203</v>
+        <v>424</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>204</v>
+        <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>106</v>
+        <v>397</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>404</v>
+        <v>232</v>
       </c>
       <c r="F13">
         <v>76</v>
@@ -11846,19 +11991,19 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>205</v>
+        <v>425</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>206</v>
+        <v>107</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>108</v>
+        <v>398</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>405</v>
+        <v>233</v>
       </c>
       <c r="F14">
         <v>63</v>
@@ -11869,19 +12014,19 @@
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>207</v>
+        <v>426</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>208</v>
+        <v>108</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>110</v>
+        <v>399</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="F15">
         <v>12</v>
@@ -11892,19 +12037,19 @@
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>209</v>
+        <v>373</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>210</v>
+        <v>109</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>149</v>
+        <v>411</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -11915,19 +12060,19 @@
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>211</v>
+        <v>427</v>
       </c>
       <c r="B17" t="s">
-        <v>212</v>
+        <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>120</v>
+        <v>404</v>
       </c>
       <c r="D17" t="s">
-        <v>143</v>
+        <v>409</v>
       </c>
       <c r="E17" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -11938,19 +12083,19 @@
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>213</v>
+        <v>361</v>
       </c>
       <c r="B18" t="s">
-        <v>214</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E18" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -11961,19 +12106,19 @@
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>428</v>
       </c>
       <c r="B19" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E19" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F19">
         <v>10</v>
@@ -11984,19 +12129,19 @@
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>349</v>
       </c>
       <c r="B20" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D20" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E20" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F20">
         <v>12</v>
@@ -12007,19 +12152,19 @@
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>219</v>
+        <v>339</v>
       </c>
       <c r="B21" t="s">
-        <v>220</v>
+        <v>114</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E21" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F21">
         <v>35</v>
@@ -12030,19 +12175,19 @@
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>221</v>
+        <v>429</v>
       </c>
       <c r="B22" t="s">
-        <v>222</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D22" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F22">
         <v>15</v>
@@ -12053,19 +12198,19 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>223</v>
+        <v>357</v>
       </c>
       <c r="B23" t="s">
-        <v>224</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D23" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E23" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F23">
         <v>20</v>
@@ -12076,19 +12221,19 @@
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>225</v>
+        <v>430</v>
       </c>
       <c r="B24" t="s">
-        <v>226</v>
+        <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D24" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E24" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F24">
         <v>25</v>
@@ -12099,19 +12244,19 @@
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>227</v>
+        <v>347</v>
       </c>
       <c r="B25" t="s">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D25" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E25" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F25">
         <v>23</v>
@@ -12122,19 +12267,19 @@
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>229</v>
+        <v>431</v>
       </c>
       <c r="B26" t="s">
-        <v>230</v>
+        <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D26" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E26" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F26">
         <v>220</v>
@@ -12145,19 +12290,19 @@
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>231</v>
+        <v>372</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D27" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E27" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F27">
         <v>43</v>
@@ -12168,19 +12313,19 @@
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>233</v>
+        <v>366</v>
       </c>
       <c r="B28" t="s">
-        <v>234</v>
+        <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D28" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E28" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F28">
         <v>212</v>
@@ -12191,19 +12336,19 @@
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>235</v>
+        <v>343</v>
       </c>
       <c r="B29" t="s">
-        <v>236</v>
+        <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D29" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F29">
         <v>210</v>
@@ -12214,19 +12359,19 @@
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>237</v>
+        <v>365</v>
       </c>
       <c r="B30" t="s">
-        <v>238</v>
+        <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E30" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F30">
         <v>80</v>
@@ -12237,19 +12382,19 @@
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>239</v>
+        <v>432</v>
       </c>
       <c r="B31" t="s">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D31" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E31" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>70</v>
@@ -12260,19 +12405,19 @@
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>348</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D32" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E32" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F32">
         <v>91</v>
@@ -12283,19 +12428,19 @@
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>243</v>
+        <v>363</v>
       </c>
       <c r="B33" t="s">
-        <v>244</v>
+        <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D33" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E33" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F33">
         <v>62</v>
@@ -12306,19 +12451,19 @@
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>245</v>
+        <v>369</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D34" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E34" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F34">
         <v>42</v>
@@ -12329,19 +12474,19 @@
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>247</v>
+        <v>346</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D35" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E35" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F35">
         <v>20</v>
@@ -12352,19 +12497,19 @@
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>249</v>
+        <v>367</v>
       </c>
       <c r="B36" t="s">
-        <v>250</v>
+        <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D36" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E36" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F36">
         <v>33</v>
@@ -12375,19 +12520,19 @@
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>251</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
+        <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D37" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E37" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F37">
         <v>22</v>
@@ -12398,19 +12543,19 @@
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>253</v>
+        <v>433</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
+        <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E38" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F38">
         <v>44</v>
@@ -12421,19 +12566,19 @@
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>255</v>
+        <v>434</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D39" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E39" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F39">
         <v>45</v>
@@ -12444,19 +12589,19 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>257</v>
+        <v>342</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E40" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F40">
         <v>98</v>
@@ -12467,19 +12612,19 @@
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>259</v>
+        <v>382</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D41" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E41" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F41">
         <v>45</v>
@@ -12490,19 +12635,19 @@
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>261</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s">
-        <v>262</v>
+        <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D42" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E42" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F42">
         <v>72</v>
@@ -12513,19 +12658,19 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>263</v>
+        <v>435</v>
       </c>
       <c r="B43" t="s">
-        <v>264</v>
+        <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D43" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E43" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F43">
         <v>320</v>
@@ -12536,19 +12681,19 @@
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>265</v>
+        <v>356</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D44" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E44" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F44">
         <v>20</v>
@@ -12559,19 +12704,19 @@
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>267</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s">
-        <v>268</v>
+        <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D45" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E45" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F45">
         <v>21</v>
@@ -12582,19 +12727,19 @@
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>269</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s">
-        <v>270</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D46" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E46" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F46">
         <v>36</v>
@@ -12605,19 +12750,19 @@
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>271</v>
+        <v>437</v>
       </c>
       <c r="B47" t="s">
-        <v>272</v>
+        <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D47" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E47" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F47">
         <v>208</v>
@@ -12628,19 +12773,19 @@
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>273</v>
+        <v>438</v>
       </c>
       <c r="B48" t="s">
-        <v>274</v>
+        <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D48" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E48" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F48">
         <v>100</v>
@@ -12651,19 +12796,19 @@
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="B49" t="s">
-        <v>276</v>
+        <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D49" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E49" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F49">
         <v>827</v>
@@ -12674,19 +12819,19 @@
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>277</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s">
-        <v>278</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D50" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E50" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F50">
         <v>923</v>
@@ -12697,19 +12842,19 @@
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>279</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s">
-        <v>280</v>
+        <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D51" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E51" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F51">
         <v>112</v>
@@ -12720,19 +12865,19 @@
     </row>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>281</v>
+        <v>340</v>
       </c>
       <c r="B52" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D52" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E52" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F52">
         <v>20</v>
@@ -12743,19 +12888,19 @@
     </row>
     <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>283</v>
+        <v>384</v>
       </c>
       <c r="B53" t="s">
-        <v>284</v>
+        <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E53" t="s">
-        <v>130</v>
+        <v>58</v>
       </c>
       <c r="F53">
         <v>1520</v>
@@ -12766,19 +12911,19 @@
     </row>
     <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>285</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s">
-        <v>286</v>
+        <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E54" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F54">
         <v>90</v>
@@ -12789,19 +12934,19 @@
     </row>
     <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>287</v>
+        <v>374</v>
       </c>
       <c r="B55" t="s">
-        <v>288</v>
+        <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E55" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F55">
         <v>99</v>
@@ -12812,19 +12957,19 @@
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>289</v>
+        <v>440</v>
       </c>
       <c r="B56" t="s">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D56" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E56" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F56">
         <v>66</v>
@@ -12835,19 +12980,19 @@
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>291</v>
+        <v>441</v>
       </c>
       <c r="B57" t="s">
-        <v>292</v>
+        <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E57" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F57">
         <v>48</v>
@@ -12858,19 +13003,19 @@
     </row>
     <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>293</v>
+        <v>442</v>
       </c>
       <c r="B58" t="s">
-        <v>294</v>
+        <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E58" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F58">
         <v>58</v>
@@ -12881,19 +13026,19 @@
     </row>
     <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>295</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s">
-        <v>296</v>
+        <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E59" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F59">
         <v>75</v>
@@ -12904,19 +13049,19 @@
     </row>
     <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>297</v>
+        <v>443</v>
       </c>
       <c r="B60" t="s">
-        <v>298</v>
+        <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D60" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E60" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F60">
         <v>95</v>
@@ -12927,19 +13072,19 @@
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>299</v>
+        <v>362</v>
       </c>
       <c r="B61" t="s">
-        <v>300</v>
+        <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D61" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F61">
         <v>65</v>
@@ -12950,19 +13095,19 @@
     </row>
     <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>301</v>
+        <v>371</v>
       </c>
       <c r="B62" t="s">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D62" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F62">
         <v>63</v>
@@ -12973,19 +13118,19 @@
     </row>
     <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>303</v>
+        <v>444</v>
       </c>
       <c r="B63" t="s">
-        <v>304</v>
+        <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D63" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E63" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F63">
         <v>62</v>
@@ -12996,19 +13141,19 @@
     </row>
     <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>305</v>
+        <v>445</v>
       </c>
       <c r="B64" t="s">
-        <v>306</v>
+        <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E64" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F64">
         <v>91</v>
@@ -13019,19 +13164,19 @@
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>307</v>
+        <v>446</v>
       </c>
       <c r="B65" t="s">
-        <v>308</v>
+        <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E65" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F65">
         <v>30</v>
@@ -13042,19 +13187,19 @@
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>309</v>
+        <v>383</v>
       </c>
       <c r="B66" t="s">
-        <v>310</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>412</v>
       </c>
       <c r="E66" t="s">
-        <v>133</v>
+        <v>61</v>
       </c>
       <c r="F66">
         <v>22</v>
@@ -13065,19 +13210,19 @@
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>311</v>
+        <v>385</v>
       </c>
       <c r="B67" t="s">
-        <v>312</v>
+        <v>160</v>
       </c>
       <c r="C67" t="s">
-        <v>118</v>
+        <v>403</v>
       </c>
       <c r="D67" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E67" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F67">
         <v>54</v>
@@ -13088,19 +13233,19 @@
     </row>
     <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="B68" t="s">
-        <v>314</v>
+        <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>120</v>
+        <v>404</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E68" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F68">
         <v>25</v>
@@ -13111,19 +13256,19 @@
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>315</v>
+        <v>447</v>
       </c>
       <c r="B69" t="s">
-        <v>316</v>
+        <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>122</v>
+        <v>405</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E69" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F69">
         <v>15</v>
@@ -13134,19 +13279,19 @@
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B70" t="s">
-        <v>318</v>
+        <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D70" t="s">
-        <v>146</v>
+        <v>410</v>
       </c>
       <c r="E70" t="s">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="F70">
         <v>68</v>
@@ -13157,19 +13302,19 @@
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>319</v>
+        <v>448</v>
       </c>
       <c r="B71" t="s">
-        <v>320</v>
+        <v>164</v>
       </c>
       <c r="C71" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="D71" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E71" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="F71">
         <v>63</v>
@@ -13180,19 +13325,19 @@
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="B72" t="s">
-        <v>322</v>
+        <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="D72" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E72" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F72">
         <v>15</v>
@@ -13203,19 +13348,19 @@
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B73" t="s">
-        <v>324</v>
+        <v>166</v>
       </c>
       <c r="C73" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="D73" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E73" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -13226,19 +13371,19 @@
     </row>
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>325</v>
+        <v>449</v>
       </c>
       <c r="B74" t="s">
-        <v>326</v>
+        <v>167</v>
       </c>
       <c r="C74" t="s">
-        <v>116</v>
+        <v>402</v>
       </c>
       <c r="D74" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E74" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F74">
         <v>25</v>
@@ -13249,19 +13394,19 @@
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
       <c r="B75" t="s">
-        <v>328</v>
+        <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D75" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E75" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F75">
         <v>61</v>
@@ -13272,19 +13417,19 @@
     </row>
     <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>329</v>
+        <v>450</v>
       </c>
       <c r="B76" t="s">
-        <v>330</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>114</v>
+        <v>458</v>
       </c>
       <c r="D76" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E76" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F76">
         <v>45</v>
@@ -13295,19 +13440,19 @@
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>331</v>
+        <v>380</v>
       </c>
       <c r="B77" t="s">
-        <v>332</v>
+        <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D77" t="s">
-        <v>137</v>
+        <v>407</v>
       </c>
       <c r="E77" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="F77">
         <v>44</v>
@@ -13318,19 +13463,19 @@
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>333</v>
+        <v>353</v>
       </c>
       <c r="B78" t="s">
-        <v>334</v>
+        <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D78" t="s">
-        <v>155</v>
+        <v>413</v>
       </c>
       <c r="E78" t="s">
-        <v>416</v>
+        <v>244</v>
       </c>
       <c r="F78">
         <v>56</v>
@@ -13341,19 +13486,19 @@
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>335</v>
+        <v>381</v>
       </c>
       <c r="B79" t="s">
-        <v>336</v>
+        <v>172</v>
       </c>
       <c r="C79" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D79" t="s">
-        <v>155</v>
+        <v>413</v>
       </c>
       <c r="E79" t="s">
-        <v>416</v>
+        <v>244</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -13364,19 +13509,19 @@
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>337</v>
+        <v>375</v>
       </c>
       <c r="B80" t="s">
-        <v>338</v>
+        <v>173</v>
       </c>
       <c r="C80" t="s">
-        <v>114</v>
+        <v>401</v>
       </c>
       <c r="D80" t="s">
-        <v>155</v>
+        <v>413</v>
       </c>
       <c r="E80" t="s">
-        <v>416</v>
+        <v>244</v>
       </c>
       <c r="F80">
         <v>212</v>
@@ -13387,19 +13532,19 @@
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>339</v>
+        <v>451</v>
       </c>
       <c r="B81" t="s">
-        <v>340</v>
+        <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>126</v>
+        <v>458</v>
       </c>
       <c r="D81" t="s">
-        <v>161</v>
+        <v>415</v>
       </c>
       <c r="E81" t="s">
-        <v>413</v>
+        <v>241</v>
       </c>
       <c r="F81">
         <v>51</v>
@@ -13410,19 +13555,19 @@
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>341</v>
+        <v>452</v>
       </c>
       <c r="B82" t="s">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>94</v>
+        <v>391</v>
       </c>
       <c r="D82" t="s">
-        <v>158</v>
+        <v>414</v>
       </c>
       <c r="E82" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="F82">
         <v>51</v>
@@ -13433,19 +13578,19 @@
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>343</v>
+        <v>453</v>
       </c>
       <c r="B83" t="s">
-        <v>344</v>
+        <v>176</v>
       </c>
       <c r="C83" t="s">
-        <v>90</v>
+        <v>389</v>
       </c>
       <c r="D83" t="s">
-        <v>164</v>
+        <v>416</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="F83">
         <v>25</v>
@@ -13456,19 +13601,19 @@
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>345</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s">
-        <v>346</v>
+        <v>177</v>
       </c>
       <c r="C84" t="s">
-        <v>94</v>
+        <v>391</v>
       </c>
       <c r="D84" t="s">
-        <v>167</v>
+        <v>417</v>
       </c>
       <c r="E84" t="s">
-        <v>128</v>
+        <v>56</v>
       </c>
       <c r="F84">
         <v>123</v>
@@ -13479,19 +13624,19 @@
     </row>
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>347</v>
+        <v>455</v>
       </c>
       <c r="B85" t="s">
-        <v>348</v>
+        <v>178</v>
       </c>
       <c r="C85" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="D85" t="s">
-        <v>170</v>
+        <v>418</v>
       </c>
       <c r="E85" t="s">
-        <v>400</v>
+        <v>228</v>
       </c>
       <c r="F85">
         <v>72</v>
@@ -13502,19 +13647,19 @@
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>349</v>
+        <v>456</v>
       </c>
       <c r="B86" t="s">
-        <v>350</v>
+        <v>179</v>
       </c>
       <c r="C86" t="s">
-        <v>120</v>
+        <v>404</v>
       </c>
       <c r="D86" t="s">
-        <v>173</v>
+        <v>419</v>
       </c>
       <c r="E86" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="F86">
         <v>155</v>
@@ -13525,19 +13670,19 @@
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>351</v>
+        <v>457</v>
       </c>
       <c r="B87" t="s">
-        <v>352</v>
+        <v>180</v>
       </c>
       <c r="C87" t="s">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="D87" t="s">
-        <v>176</v>
+        <v>420</v>
       </c>
       <c r="E87" t="s">
-        <v>131</v>
+        <v>59</v>
       </c>
       <c r="F87">
         <v>200</v>

--- a/Database/Data.xlsx
+++ b/Database/Data.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/867b96fdabfe5cc4/Ubuntu/CongNghePhanMem/BookStoreManagement/Database/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8FEB9D8DC7A054F8B33F543BBE935DD73E6C2F80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CB3F26B9-6938-4A83-93E2-B97CF488406E}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="11_8FEB9D8DC7A054F8B33F543BBE935DD73E6C2F80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3FB12E6-E6FB-4F87-9EC2-C8962B126979}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Account" sheetId="2" r:id="rId1"/>
     <sheet name="Staff" sheetId="10" r:id="rId2"/>
-    <sheet name="Bill" sheetId="3" r:id="rId3"/>
-    <sheet name="BillDetail" sheetId="9" r:id="rId4"/>
+    <sheet name="Delivery" sheetId="11" r:id="rId3"/>
+    <sheet name="Bill" sheetId="3" r:id="rId4"/>
     <sheet name="Author" sheetId="4" r:id="rId5"/>
     <sheet name="Publisher" sheetId="6" r:id="rId6"/>
     <sheet name="Book" sheetId="7" r:id="rId7"/>
+    <sheet name="BillDetail" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -161,71 +162,6 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Arial"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>======
-ID#AAAAkN7UZeI
-Hoàng Minh    (2022-11-19 21:04:58)
-Một hóa đơn sẽ gồm nhiều mặt hàng, trong trường hợp này là nhiều loại sách, bảng này mô tả các mặt hàng đó
-BillID là khóa ngoại
-khóa của bảng này là cặp (BillID, BookID) vì thế không được có 2 cặp (BillID, BookID) nào giống nhau</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Arial"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>======
-ID#AAAAkN7UZe8
-Hoàng Minh    (2022-11-19 21:04:58)
-BookID là khóa ngoại</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Arial"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>======
-ID#AAAAkN7UZeg
-Hoàng Minh    (2022-11-19 21:04:58)
-số lượng sách có trong hóa đơn</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-  <extLst>
-    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion1">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mj86gE51oUu6vbRLrYso25/qW3xvg=="/>
-    </ext>
-  </extLst>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author/>
-  </authors>
-  <commentList>
     <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
@@ -252,7 +188,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
@@ -347,8 +283,73 @@
 </comments>
 </file>
 
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAAkN7UZeI
+Hoàng Minh    (2022-11-19 21:04:58)
+Một hóa đơn sẽ gồm nhiều mặt hàng, trong trường hợp này là nhiều loại sách, bảng này mô tả các mặt hàng đó
+BillID là khóa ngoại
+khóa của bảng này là cặp (BillID, BookID) vì thế không được có 2 cặp (BillID, BookID) nào giống nhau</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAAkN7UZe8
+Hoàng Minh    (2022-11-19 21:04:58)
+BookID là khóa ngoại</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Arial"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>======
+ID#AAAAkN7UZeg
+Hoàng Minh    (2022-11-19 21:04:58)
+số lượng sách có trong hóa đơn</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+  <extLst>
+    <ext xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" uri="GoogleSheetsCustomDataVersion1">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mj86gE51oUu6vbRLrYso25/qW3xvg=="/>
+    </ext>
+  </extLst>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="954" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="487">
   <si>
     <t>Name</t>
   </si>
@@ -899,36 +900,6 @@
     <t>UnitPrice</t>
   </si>
   <si>
-    <t>0818704559</t>
-  </si>
-  <si>
-    <t>0239936536</t>
-  </si>
-  <si>
-    <t>0718225689</t>
-  </si>
-  <si>
-    <t>0871171047</t>
-  </si>
-  <si>
-    <t>0491735142</t>
-  </si>
-  <si>
-    <t>0802342079</t>
-  </si>
-  <si>
-    <t>0114656132</t>
-  </si>
-  <si>
-    <t>0126459679</t>
-  </si>
-  <si>
-    <t>0862452688</t>
-  </si>
-  <si>
-    <t>0372827009</t>
-  </si>
-  <si>
     <t>dinhbatien_UID01@gmail.com</t>
   </si>
   <si>
@@ -980,12 +951,6 @@
     <t>0800983798</t>
   </si>
   <si>
-    <t>0982297546</t>
-  </si>
-  <si>
-    <t>0855373189</t>
-  </si>
-  <si>
     <t>0643649162</t>
   </si>
   <si>
@@ -1091,12 +1056,6 @@
     <t>Đinh Trọng Tiến</t>
   </si>
   <si>
-    <t>0266457362</t>
-  </si>
-  <si>
-    <t>0265685365</t>
-  </si>
-  <si>
     <t>223 Nguyễn Văn Cừ, Tp HCM</t>
   </si>
   <si>
@@ -1148,9 +1107,6 @@
     <t>Đinh Bá Tùng</t>
   </si>
   <si>
-    <t>0818704548</t>
-  </si>
-  <si>
     <t>dinhbatung_UID01@gmail.com</t>
   </si>
   <si>
@@ -1160,9 +1116,6 @@
     <t>Lê Quỳnh Nhung</t>
   </si>
   <si>
-    <t>0871171036</t>
-  </si>
-  <si>
     <t>lequynhnhung_UID04@gmail.com</t>
   </si>
   <si>
@@ -1190,9 +1143,6 @@
     <t>Nguyễn Xuân Thông</t>
   </si>
   <si>
-    <t>0862452677</t>
-  </si>
-  <si>
     <t>nguyenxuanthong_UID09@gmail.com</t>
   </si>
   <si>
@@ -1725,13 +1675,148 @@
   </si>
   <si>
     <t>AuID0016</t>
+  </si>
+  <si>
+    <t>"0818704548"</t>
+  </si>
+  <si>
+    <t>"0818704559"</t>
+  </si>
+  <si>
+    <t>"0239936536"</t>
+  </si>
+  <si>
+    <t>"0266457362"</t>
+  </si>
+  <si>
+    <t>"0265685365"</t>
+  </si>
+  <si>
+    <t>"0718225689"</t>
+  </si>
+  <si>
+    <t>"0871171036"</t>
+  </si>
+  <si>
+    <t>"0871171047"</t>
+  </si>
+  <si>
+    <t>"0491735142"</t>
+  </si>
+  <si>
+    <t>"0802342079"</t>
+  </si>
+  <si>
+    <t>"0114656132"</t>
+  </si>
+  <si>
+    <t>"0126459679"</t>
+  </si>
+  <si>
+    <t>"0862452677"</t>
+  </si>
+  <si>
+    <t>"0862452688"</t>
+  </si>
+  <si>
+    <t>"0372827009"</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>Delivery</t>
+  </si>
+  <si>
+    <t>DeliveryID</t>
+  </si>
+  <si>
+    <t>DID0001</t>
+  </si>
+  <si>
+    <t>DID0002</t>
+  </si>
+  <si>
+    <t>DID0003</t>
+  </si>
+  <si>
+    <t>DID0004</t>
+  </si>
+  <si>
+    <t>DID0005</t>
+  </si>
+  <si>
+    <t>DID0006</t>
+  </si>
+  <si>
+    <t>DID0007</t>
+  </si>
+  <si>
+    <t>DID0008</t>
+  </si>
+  <si>
+    <t>Grab Express Delivery</t>
+  </si>
+  <si>
+    <t>Viettel Post</t>
+  </si>
+  <si>
+    <t>J&amp;T Express</t>
+  </si>
+  <si>
+    <t>Ahamove</t>
+  </si>
+  <si>
+    <t>Lalamove</t>
+  </si>
+  <si>
+    <t>Giao hàng nhanh</t>
+  </si>
+  <si>
+    <t>Giao hàng tiết kiệm</t>
+  </si>
+  <si>
+    <t>Nhất Tín logistics</t>
+  </si>
+  <si>
+    <t>Fee</t>
+  </si>
+  <si>
+    <t>"0982297546"</t>
+  </si>
+  <si>
+    <t>"0855373189"</t>
+  </si>
+  <si>
+    <t>0987790790</t>
+  </si>
+  <si>
+    <t>0987790791</t>
+  </si>
+  <si>
+    <t>0987790792</t>
+  </si>
+  <si>
+    <t>0987790793</t>
+  </si>
+  <si>
+    <t>0987790794</t>
+  </si>
+  <si>
+    <t>0987790795</t>
+  </si>
+  <si>
+    <t>0987790796</t>
+  </si>
+  <si>
+    <t>0987790797</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1838,6 +1923,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1860,7 +1952,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1890,6 +1982,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1933,6 +2029,14 @@
 </file>
 
 <file path=xl/persons/person5.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person6.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
+<file path=xl/persons/person7.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
@@ -2142,7 +2246,7 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="8.625" customWidth="1"/>
     <col min="5" max="5" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="26.375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="34.5" bestFit="1" customWidth="1"/>
     <col min="9" max="24" width="8.625" customWidth="1"/>
@@ -2176,33 +2280,33 @@
     </row>
     <row r="2" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="22" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>272</v>
+        <v>256</v>
       </c>
       <c r="C2" t="s">
-        <v>273</v>
+        <v>257</v>
       </c>
       <c r="D2" s="22" t="s">
         <v>28</v>
       </c>
       <c r="E2" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>266</v>
+        <v>442</v>
       </c>
       <c r="G2" t="s">
-        <v>264</v>
+        <v>250</v>
       </c>
       <c r="H2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="11" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B3" s="10" t="str">
         <f>A3&amp;D3</f>
@@ -2219,18 +2323,18 @@
         <v>4</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>183</v>
+        <v>443</v>
       </c>
       <c r="G3" t="s">
         <v>5</v>
       </c>
       <c r="H3" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="11" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="B4" s="10" t="str">
         <f t="shared" ref="B4:B16" si="0">A4&amp;D4</f>
@@ -2247,18 +2351,18 @@
         <v>6</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>184</v>
+        <v>444</v>
       </c>
       <c r="G4" t="s">
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B5" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2272,21 +2376,21 @@
         <v>28</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>247</v>
+        <v>445</v>
       </c>
       <c r="G5" t="s">
-        <v>249</v>
+        <v>235</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>251</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B6" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2300,21 +2404,21 @@
         <v>28</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>248</v>
+        <v>446</v>
       </c>
       <c r="G6" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>252</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="11" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B7" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2331,44 +2435,44 @@
         <v>8</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>185</v>
+        <v>447</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="24" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>274</v>
+        <v>258</v>
       </c>
       <c r="C8" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="D8" s="24" t="s">
         <v>29</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>270</v>
+        <v>448</v>
       </c>
       <c r="G8" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="H8" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="B9" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2385,18 +2489,18 @@
         <v>10</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>186</v>
+        <v>449</v>
       </c>
       <c r="G9" t="s">
         <v>11</v>
       </c>
       <c r="H9" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="11" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B10" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2413,18 +2517,18 @@
         <v>12</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>187</v>
+        <v>450</v>
       </c>
       <c r="G10" t="s">
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="11" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="B11" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2441,18 +2545,18 @@
         <v>14</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>188</v>
+        <v>451</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="B12" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2469,18 +2573,18 @@
         <v>16</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>189</v>
+        <v>452</v>
       </c>
       <c r="G12" t="s">
         <v>17</v>
       </c>
       <c r="H12" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="B13" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2497,44 +2601,44 @@
         <v>18</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>190</v>
+        <v>453</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>276</v>
+        <v>260</v>
       </c>
       <c r="C14" t="s">
-        <v>277</v>
+        <v>261</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>30</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>280</v>
+        <v>454</v>
       </c>
       <c r="G14" t="s">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="H14" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="11" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="B15" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2551,18 +2655,18 @@
         <v>20</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>191</v>
+        <v>455</v>
       </c>
       <c r="G15" t="s">
         <v>21</v>
       </c>
       <c r="H15" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="B16" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2579,13 +2683,13 @@
         <v>22</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>192</v>
+        <v>456</v>
       </c>
       <c r="G16" t="s">
         <v>23</v>
       </c>
       <c r="H16" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3591,7 +3695,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="10.625" bestFit="1" customWidth="1"/>
@@ -3600,13 +3704,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>32</v>
@@ -3614,13 +3718,13 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="B2">
         <v>7360000</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D2" s="19">
         <v>45174</v>
@@ -3629,13 +3733,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="B3">
         <v>6430000</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>257</v>
+        <v>243</v>
       </c>
       <c r="D3" s="19">
         <v>45107</v>
@@ -3644,13 +3748,13 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="B4">
         <v>4780000</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D4" s="20">
         <v>45091</v>
@@ -3659,13 +3763,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B5">
         <v>4540000</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="D5" s="19">
         <v>44955</v>
@@ -3674,13 +3778,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
       <c r="B6">
         <v>7160000</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="D6" s="19">
         <v>45048</v>
@@ -3688,23 +3792,23 @@
       <c r="E6" s="21"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
-        <v>295</v>
+      <c r="A7" t="s">
+        <v>265</v>
       </c>
       <c r="B7">
         <v>7160000</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>30</v>
+        <v>242</v>
       </c>
       <c r="D7" s="19">
-        <v>44954</v>
+        <v>45049</v>
       </c>
       <c r="E7" s="21"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B8">
         <v>7160000</v>
@@ -3713,672 +3817,1092 @@
         <v>30</v>
       </c>
       <c r="D8" s="19">
+        <v>44954</v>
+      </c>
+      <c r="E8" s="21"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>279</v>
+      </c>
+      <c r="B9">
+        <v>7160000</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="19">
         <v>44932</v>
       </c>
-      <c r="E8" s="21"/>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10">
+        <v>7000000</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" s="19">
+        <v>44933</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C83E110C-B3BD-4C81-BA77-F712E07525B6}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="26.625" customWidth="1"/>
+    <col min="4" max="4" width="10.875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>468</v>
+      </c>
+      <c r="C2">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>469</v>
+      </c>
+      <c r="C3">
+        <v>20000</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5">
+        <v>12000</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>472</v>
+      </c>
+      <c r="C6">
+        <v>14000</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>473</v>
+      </c>
+      <c r="C7">
+        <v>15000</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>474</v>
+      </c>
+      <c r="C8">
+        <v>16000</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>475</v>
+      </c>
+      <c r="C9">
+        <v>17000</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>486</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:G1000"/>
+  <dimension ref="A1:H1000"/>
   <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="3" max="3" width="9.875" customWidth="1"/>
-    <col min="4" max="26" width="8.625" customWidth="1"/>
+    <col min="2" max="3" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="9.875" customWidth="1"/>
+    <col min="5" max="27" width="8.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="22" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E1" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2" s="2">
+        <v>44885</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F2" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="2">
+        <v>44886</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D4" s="2">
+        <v>44887</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B5" t="s">
+        <v>273</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" s="2">
+        <v>44888</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F5" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D6" s="2">
+        <v>44889</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B7" t="s">
+        <v>274</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D7" s="2">
+        <v>44890</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F7" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" s="2">
+        <v>44891</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="2">
+        <v>44892</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B10" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="2">
+        <v>44893</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B11" t="s">
+        <v>275</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D11" s="2">
+        <v>44894</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F11" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D12" s="2">
+        <v>44895</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F12" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D13" s="2">
+        <v>44896</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="2">
+        <v>44897</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F14" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D15" s="2">
+        <v>44898</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D16" s="2">
+        <v>44899</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F16" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="B17" t="s">
+        <v>274</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="2">
+        <v>44900</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D18" s="2">
+        <v>44901</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" s="2">
-        <v>44885</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="B19" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D19" s="2">
+        <v>44902</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F19" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="2">
-        <v>44886</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="B20" t="s">
+        <v>273</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="2">
+        <v>44903</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F20" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C4" s="2">
-        <v>44887</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="B21" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D21" s="2">
+        <v>44904</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F21" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
         <v>300</v>
       </c>
-      <c r="B5" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="2">
-        <v>44888</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="B22" t="s">
+        <v>274</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="2">
+        <v>44905</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F22" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C6" s="2">
-        <v>44889</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="B23" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D23" s="2">
+        <v>44906</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>302</v>
       </c>
-      <c r="B7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C7" s="2">
-        <v>44890</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="B24" t="s">
+        <v>276</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="2">
+        <v>44907</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C8" s="2">
-        <v>44891</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="B25" t="s">
+        <v>275</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D25" s="2">
+        <v>44908</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F25" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B9" t="s">
-        <v>293</v>
-      </c>
-      <c r="C9" s="2">
-        <v>44892</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="B26" t="s">
+        <v>275</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D26" s="2">
+        <v>44909</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F26" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="B10" t="s">
-        <v>292</v>
-      </c>
-      <c r="C10" s="2">
-        <v>44893</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="B27" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" s="2">
+        <v>44910</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="B11" t="s">
-        <v>292</v>
-      </c>
-      <c r="C11" s="2">
-        <v>44894</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D28" s="2">
+        <v>44911</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>307</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="2">
-        <v>44895</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
+      <c r="B29" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D29" s="2">
+        <v>44912</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F29" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C13" s="2">
-        <v>44896</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
+      <c r="B30" t="s">
+        <v>273</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D30" s="2">
+        <v>44913</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
         <v>309</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C14" s="2">
-        <v>44897</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
+      <c r="B31" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D31" s="2">
+        <v>44914</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="B15" t="s">
-        <v>290</v>
-      </c>
-      <c r="C15" s="2">
-        <v>44898</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
+      <c r="B32" t="s">
+        <v>274</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D32" s="2">
+        <v>44915</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F32" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C16" s="2">
-        <v>44899</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
+      <c r="B33" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D33" s="2">
+        <v>44916</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F33" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="B17" t="s">
-        <v>291</v>
-      </c>
-      <c r="C17" s="2">
-        <v>44900</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
+      <c r="B34" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D34" s="2">
+        <v>44917</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F34" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C18" s="2">
-        <v>44901</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
+      <c r="B35" t="s">
+        <v>273</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D35" s="2">
+        <v>44918</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F35" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>314</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C19" s="2">
-        <v>44902</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
+      <c r="B36" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D36" s="2">
+        <v>44919</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F36" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B20" t="s">
-        <v>290</v>
-      </c>
-      <c r="C20" s="2">
-        <v>44903</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
+      <c r="B37" t="s">
+        <v>274</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D37" s="2">
+        <v>44920</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C21" s="2">
-        <v>44904</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
+      <c r="B38" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D38" s="2">
+        <v>44921</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="F38" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>317</v>
       </c>
-      <c r="B22" t="s">
-        <v>291</v>
-      </c>
-      <c r="C22" s="2">
-        <v>44905</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
+      <c r="B39" t="s">
+        <v>276</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="2">
+        <v>44922</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F39" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C23" s="2">
-        <v>44906</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
+      <c r="B40" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D40" s="2">
+        <v>44923</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="F40" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="B24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C24" s="2">
-        <v>44907</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B25" t="s">
-        <v>292</v>
-      </c>
-      <c r="C25" s="2">
-        <v>44908</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B26" t="s">
-        <v>292</v>
-      </c>
-      <c r="C26" s="2">
-        <v>44909</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C27" s="2">
-        <v>44910</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C28" s="2">
-        <v>44911</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C29" s="2">
-        <v>44912</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="B30" t="s">
-        <v>290</v>
-      </c>
-      <c r="C30" s="2">
-        <v>44913</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C31" s="2">
-        <v>44914</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="B32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C32" s="2">
-        <v>44915</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C33" s="2">
-        <v>44916</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="C34" s="2">
-        <v>44917</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="B35" t="s">
-        <v>290</v>
-      </c>
-      <c r="C35" s="2">
-        <v>44918</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C36" s="2">
-        <v>44919</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B37" t="s">
-        <v>291</v>
-      </c>
-      <c r="C37" s="2">
-        <v>44920</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C38" s="2">
-        <v>44921</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="B39" t="s">
-        <v>293</v>
-      </c>
-      <c r="C39" s="2">
-        <v>44922</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="B40" t="s">
-        <v>292</v>
-      </c>
-      <c r="C40" s="2">
-        <v>44923</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="B41" t="s">
-        <v>292</v>
-      </c>
-      <c r="C41" s="2">
+        <v>275</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="D41" s="2">
         <v>44924</v>
       </c>
-      <c r="D41" s="1" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E41" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="F41" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="1"/>
-    </row>
-    <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C42" s="1"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="1"/>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="1"/>
-      <c r="G43" t="str">
-        <f xml:space="preserve"> LOWER(F43)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C43" s="1"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="1"/>
+    </row>
+    <row r="44" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="4"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="1"/>
-      <c r="G44" t="str">
-        <f xml:space="preserve"> LOWER(F44)</f>
+      <c r="C44" s="4"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="1"/>
+      <c r="H44" t="str">
+        <f xml:space="preserve"> LOWER(G44)</f>
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="1"/>
-    </row>
-    <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D45" s="2"/>
+      <c r="E45" s="1"/>
+    </row>
+    <row r="46" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="4"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="1"/>
-    </row>
-    <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C46" s="4"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="1"/>
-    </row>
-    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D47" s="2"/>
+      <c r="E47" s="1"/>
+    </row>
+    <row r="48" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="1"/>
-    </row>
-    <row r="49" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C48" s="1"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="1"/>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="4"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="1"/>
-    </row>
-    <row r="50" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C50" s="2"/>
-      <c r="D50" s="1"/>
-    </row>
-    <row r="51" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="C49" s="4"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="1"/>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D50" s="2"/>
+      <c r="E50" s="1"/>
+    </row>
+    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="54" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="56" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="58" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="59" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="63" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="64" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -5323,1959 +5847,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C1006"/>
-  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="8.625" customWidth="1"/>
-    <col min="2" max="2" width="9.5" customWidth="1"/>
-    <col min="3" max="3" width="7.625" customWidth="1"/>
-    <col min="4" max="26" width="8.625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="B2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C2" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" t="s">
-        <v>338</v>
-      </c>
-      <c r="C3" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="str">
-        <f>A3</f>
-        <v>BiID0002</v>
-      </c>
-      <c r="B4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B5" t="s">
-        <v>340</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="B6" t="s">
-        <v>341</v>
-      </c>
-      <c r="C6" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>342</v>
-      </c>
-      <c r="C7" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C8" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="str">
-        <f>A8</f>
-        <v>BiID0003</v>
-      </c>
-      <c r="B9" t="s">
-        <v>344</v>
-      </c>
-      <c r="C9" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B10" t="s">
-        <v>345</v>
-      </c>
-      <c r="C10" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" t="s">
-        <v>346</v>
-      </c>
-      <c r="C11" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B12" t="s">
-        <v>347</v>
-      </c>
-      <c r="C12" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B13" t="s">
-        <v>348</v>
-      </c>
-      <c r="C13" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="str">
-        <f>A12</f>
-        <v>BiID0005</v>
-      </c>
-      <c r="B14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C14" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B15" t="s">
-        <v>350</v>
-      </c>
-      <c r="C15" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B16" t="s">
-        <v>351</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B17" t="s">
-        <v>341</v>
-      </c>
-      <c r="C17" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="B18" t="s">
-        <v>352</v>
-      </c>
-      <c r="C18" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B19" t="s">
-        <v>353</v>
-      </c>
-      <c r="C19" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B20" t="s">
-        <v>354</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="B21" t="s">
-        <v>342</v>
-      </c>
-      <c r="C21" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B22" t="s">
-        <v>355</v>
-      </c>
-      <c r="C22" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B23" t="s">
-        <v>356</v>
-      </c>
-      <c r="C23" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B24" t="s">
-        <v>357</v>
-      </c>
-      <c r="C24" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B25" t="s">
-        <v>348</v>
-      </c>
-      <c r="C25" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B26" t="s">
-        <v>350</v>
-      </c>
-      <c r="C26" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B27" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B28" t="s">
-        <v>359</v>
-      </c>
-      <c r="C28" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B29" t="s">
-        <v>344</v>
-      </c>
-      <c r="C29" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B30" t="s">
-        <v>360</v>
-      </c>
-      <c r="C30" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="B31" t="s">
-        <v>361</v>
-      </c>
-      <c r="C31" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="B32" t="s">
-        <v>353</v>
-      </c>
-      <c r="C32" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B33" t="s">
-        <v>362</v>
-      </c>
-      <c r="C33" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B34" t="s">
-        <v>363</v>
-      </c>
-      <c r="C34" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B35" t="s">
-        <v>364</v>
-      </c>
-      <c r="C35" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B36" t="s">
-        <v>365</v>
-      </c>
-      <c r="C36" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="B37" t="s">
-        <v>366</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B38" t="s">
-        <v>367</v>
-      </c>
-      <c r="C38" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B39" t="s">
-        <v>368</v>
-      </c>
-      <c r="C39" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B40" t="s">
-        <v>369</v>
-      </c>
-      <c r="C40" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B41" t="s">
-        <v>370</v>
-      </c>
-      <c r="C41" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B42" t="s">
-        <v>371</v>
-      </c>
-      <c r="C42" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="B43" t="s">
-        <v>372</v>
-      </c>
-      <c r="C43" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="B44" t="s">
-        <v>373</v>
-      </c>
-      <c r="C44" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B45" t="s">
-        <v>361</v>
-      </c>
-      <c r="C45" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B46" t="s">
-        <v>374</v>
-      </c>
-      <c r="C46" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B47" t="s">
-        <v>363</v>
-      </c>
-      <c r="C47" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B48" t="s">
-        <v>371</v>
-      </c>
-      <c r="C48" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B49" t="s">
-        <v>375</v>
-      </c>
-      <c r="C49" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B50" t="s">
-        <v>353</v>
-      </c>
-      <c r="C50" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B51" t="s">
-        <v>376</v>
-      </c>
-      <c r="C51" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B52" t="s">
-        <v>377</v>
-      </c>
-      <c r="C52" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B53" t="s">
-        <v>340</v>
-      </c>
-      <c r="C53" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="B54" t="s">
-        <v>378</v>
-      </c>
-      <c r="C54" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="C55" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="C56" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="C57" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C58" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C59" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C60" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C62" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="C63" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="C64" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="C65" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C66" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C67" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="C68" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="C69" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B70" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="C70" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="C71" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C72" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="C73" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="C74" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C75" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="4" t="str">
-        <f>A77</f>
-        <v>BiID0039</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="C76" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C77" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="C78" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C79" s="1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="C80" s="1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="4"/>
-      <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
-    </row>
-    <row r="85" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-    </row>
-    <row r="88" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-    </row>
-    <row r="89" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-    </row>
-    <row r="91" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
-    </row>
-    <row r="92" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-    </row>
-    <row r="93" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-    </row>
-    <row r="94" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-    </row>
-    <row r="95" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-    </row>
-    <row r="97" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B97" s="1"/>
-    </row>
-    <row r="98" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B98" s="1"/>
-    </row>
-    <row r="99" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B99" s="1"/>
-    </row>
-    <row r="100" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B100" s="1"/>
-    </row>
-    <row r="101" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B101" s="1"/>
-    </row>
-    <row r="102" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B102" s="1"/>
-    </row>
-    <row r="103" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B103" s="1"/>
-    </row>
-    <row r="104" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B104" s="1"/>
-    </row>
-    <row r="105" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B105" s="1"/>
-    </row>
-    <row r="106" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B106" s="1"/>
-    </row>
-    <row r="107" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B107" s="1"/>
-    </row>
-    <row r="108" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B108" s="1"/>
-    </row>
-    <row r="109" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B109" s="1"/>
-    </row>
-    <row r="110" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B110" s="1"/>
-    </row>
-    <row r="111" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B111" s="1"/>
-    </row>
-    <row r="112" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B112" s="1"/>
-    </row>
-    <row r="113" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B113" s="1"/>
-    </row>
-    <row r="114" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B114" s="1"/>
-    </row>
-    <row r="115" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B115" s="1"/>
-    </row>
-    <row r="116" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B116" s="1"/>
-    </row>
-    <row r="117" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B117" s="1"/>
-    </row>
-    <row r="118" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B118" s="1"/>
-    </row>
-    <row r="119" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B119" s="1"/>
-    </row>
-    <row r="120" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B120" s="1"/>
-    </row>
-    <row r="121" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B121" s="1"/>
-    </row>
-    <row r="122" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B122" s="1"/>
-    </row>
-    <row r="123" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B123" s="1"/>
-    </row>
-    <row r="124" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="1"/>
-    </row>
-    <row r="125" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="1"/>
-    </row>
-    <row r="126" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B126" s="1"/>
-    </row>
-    <row r="127" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B127" s="1"/>
-    </row>
-    <row r="128" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B128" s="1"/>
-    </row>
-    <row r="129" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B129" s="1"/>
-    </row>
-    <row r="130" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B130" s="1"/>
-    </row>
-    <row r="131" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B132" s="1"/>
-    </row>
-    <row r="133" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B133" s="1"/>
-    </row>
-    <row r="134" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A80">
-    <sortCondition ref="A2:A80"/>
-  </sortState>
-  <phoneticPr fontId="14" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
-  <legacyDrawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:C1000"/>
@@ -7300,244 +5871,244 @@
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="B2" t="s">
         <v>34</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="B3" t="s">
         <v>35</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="B4" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B5" t="s">
         <v>37</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="B6" t="s">
         <v>38</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="B7" t="s">
         <v>39</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="B8" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="B9" t="s">
         <v>41</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>210</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="B10" t="s">
         <v>42</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>211</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="16" t="s">
-        <v>212</v>
+      <c r="C11" s="26" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="B12" t="s">
         <v>44</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="B13" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="B14" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B17" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="B18" t="s">
         <v>50</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="B19" t="s">
         <v>51</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="B20" s="12" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="B21" t="s">
         <v>53</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="B22" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="B23" t="s">
         <v>55</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -8549,7 +7120,7 @@
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>65</v>
@@ -8560,7 +7131,7 @@
     </row>
     <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>67</v>
@@ -8571,7 +7142,7 @@
     </row>
     <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>69</v>
@@ -8582,7 +7153,7 @@
     </row>
     <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>71</v>
@@ -8593,7 +7164,7 @@
     </row>
     <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>73</v>
@@ -8604,7 +7175,7 @@
     </row>
     <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="B7" t="s">
         <v>75</v>
@@ -8615,7 +7186,7 @@
     </row>
     <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="B8" t="s">
         <v>77</v>
@@ -8626,7 +7197,7 @@
     </row>
     <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="B9" t="s">
         <v>79</v>
@@ -8637,7 +7208,7 @@
     </row>
     <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="B10" t="s">
         <v>81</v>
@@ -8648,7 +7219,7 @@
     </row>
     <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>83</v>
@@ -8659,7 +7230,7 @@
     </row>
     <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>85</v>
@@ -8670,7 +7241,7 @@
     </row>
     <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="B13" t="s">
         <v>87</v>
@@ -8681,7 +7252,7 @@
     </row>
     <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>89</v>
@@ -8692,7 +7263,7 @@
     </row>
     <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="B15" t="s">
         <v>91</v>
@@ -11704,7 +10275,7 @@
         <v>62</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>259</v>
+        <v>245</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>181</v>
@@ -11715,19 +10286,19 @@
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="B2" t="s">
         <v>95</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="F2" s="1">
         <v>15</v>
@@ -11738,19 +10309,19 @@
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="B3" t="s">
         <v>96</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="D3" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="F3" s="1">
         <v>58</v>
@@ -11761,19 +10332,19 @@
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>97</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -11784,19 +10355,19 @@
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>422</v>
+        <v>405</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>98</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F5">
         <v>42</v>
@@ -11807,19 +10378,19 @@
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="B6" t="s">
         <v>99</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="F6">
         <v>36</v>
@@ -11830,19 +10401,19 @@
     </row>
     <row r="7" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>423</v>
+        <v>406</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>408</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="F7">
         <v>68</v>
@@ -11853,19 +10424,19 @@
     </row>
     <row r="8" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>408</v>
+        <v>391</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="F8">
         <v>79</v>
@@ -11876,19 +10447,19 @@
     </row>
     <row r="9" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F9">
         <v>82</v>
@@ -11899,19 +10470,19 @@
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F10">
         <v>30</v>
@@ -11922,19 +10493,19 @@
     </row>
     <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="F11">
         <v>24</v>
@@ -11945,19 +10516,19 @@
     </row>
     <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="F12">
         <v>28</v>
@@ -11968,19 +10539,19 @@
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>424</v>
+        <v>407</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>106</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
       <c r="D13" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="F13">
         <v>76</v>
@@ -11991,19 +10562,19 @@
     </row>
     <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>107</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="D14" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="F14">
         <v>63</v>
@@ -12014,19 +10585,19 @@
     </row>
     <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>426</v>
+        <v>409</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="F15">
         <v>12</v>
@@ -12037,19 +10608,19 @@
     </row>
     <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="F16">
         <v>10</v>
@@ -12060,19 +10631,19 @@
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>427</v>
+        <v>410</v>
       </c>
       <c r="B17" t="s">
         <v>110</v>
       </c>
       <c r="C17" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D17" t="s">
-        <v>409</v>
+        <v>392</v>
       </c>
       <c r="E17" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="F17">
         <v>12</v>
@@ -12083,16 +10654,16 @@
     </row>
     <row r="18" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="B18" t="s">
         <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D18" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E18" t="s">
         <v>58</v>
@@ -12106,16 +10677,16 @@
     </row>
     <row r="19" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="B19" t="s">
         <v>112</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D19" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E19" t="s">
         <v>58</v>
@@ -12129,16 +10700,16 @@
     </row>
     <row r="20" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B20" t="s">
         <v>113</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D20" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E20" t="s">
         <v>58</v>
@@ -12152,16 +10723,16 @@
     </row>
     <row r="21" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>339</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s">
         <v>114</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D21" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E21" t="s">
         <v>58</v>
@@ -12175,16 +10746,16 @@
     </row>
     <row r="22" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>429</v>
+        <v>412</v>
       </c>
       <c r="B22" t="s">
         <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D22" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E22" t="s">
         <v>58</v>
@@ -12198,16 +10769,16 @@
     </row>
     <row r="23" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="B23" t="s">
         <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D23" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E23" t="s">
         <v>58</v>
@@ -12221,16 +10792,16 @@
     </row>
     <row r="24" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>430</v>
+        <v>413</v>
       </c>
       <c r="B24" t="s">
         <v>117</v>
       </c>
       <c r="C24" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D24" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E24" t="s">
         <v>58</v>
@@ -12244,16 +10815,16 @@
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="B25" t="s">
         <v>118</v>
       </c>
       <c r="C25" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D25" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E25" t="s">
         <v>58</v>
@@ -12267,16 +10838,16 @@
     </row>
     <row r="26" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>431</v>
+        <v>414</v>
       </c>
       <c r="B26" t="s">
         <v>119</v>
       </c>
       <c r="C26" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D26" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E26" t="s">
         <v>58</v>
@@ -12290,16 +10861,16 @@
     </row>
     <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="B27" t="s">
         <v>120</v>
       </c>
       <c r="C27" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D27" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E27" t="s">
         <v>58</v>
@@ -12313,16 +10884,16 @@
     </row>
     <row r="28" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B28" t="s">
         <v>121</v>
       </c>
       <c r="C28" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D28" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E28" t="s">
         <v>58</v>
@@ -12336,16 +10907,16 @@
     </row>
     <row r="29" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="B29" t="s">
         <v>122</v>
       </c>
       <c r="C29" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D29" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E29" t="s">
         <v>58</v>
@@ -12359,16 +10930,16 @@
     </row>
     <row r="30" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
       <c r="B30" t="s">
         <v>123</v>
       </c>
       <c r="C30" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D30" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E30" t="s">
         <v>58</v>
@@ -12382,16 +10953,16 @@
     </row>
     <row r="31" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>432</v>
+        <v>415</v>
       </c>
       <c r="B31" t="s">
         <v>124</v>
       </c>
       <c r="C31" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D31" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E31" t="s">
         <v>58</v>
@@ -12405,16 +10976,16 @@
     </row>
     <row r="32" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s">
         <v>125</v>
       </c>
       <c r="C32" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D32" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E32" t="s">
         <v>58</v>
@@ -12428,16 +10999,16 @@
     </row>
     <row r="33" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
       <c r="B33" t="s">
         <v>126</v>
       </c>
       <c r="C33" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D33" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E33" t="s">
         <v>58</v>
@@ -12451,16 +11022,16 @@
     </row>
     <row r="34" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
       <c r="B34" t="s">
         <v>127</v>
       </c>
       <c r="C34" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D34" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E34" t="s">
         <v>58</v>
@@ -12474,16 +11045,16 @@
     </row>
     <row r="35" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="B35" t="s">
         <v>128</v>
       </c>
       <c r="C35" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D35" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E35" t="s">
         <v>58</v>
@@ -12497,16 +11068,16 @@
     </row>
     <row r="36" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s">
         <v>129</v>
       </c>
       <c r="C36" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D36" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E36" t="s">
         <v>58</v>
@@ -12520,16 +11091,16 @@
     </row>
     <row r="37" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B37" t="s">
         <v>130</v>
       </c>
       <c r="C37" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D37" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E37" t="s">
         <v>58</v>
@@ -12543,16 +11114,16 @@
     </row>
     <row r="38" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>433</v>
+        <v>416</v>
       </c>
       <c r="B38" t="s">
         <v>131</v>
       </c>
       <c r="C38" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D38" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E38" t="s">
         <v>58</v>
@@ -12566,16 +11137,16 @@
     </row>
     <row r="39" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>434</v>
+        <v>417</v>
       </c>
       <c r="B39" t="s">
         <v>132</v>
       </c>
       <c r="C39" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D39" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E39" t="s">
         <v>58</v>
@@ -12589,16 +11160,16 @@
     </row>
     <row r="40" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s">
         <v>133</v>
       </c>
       <c r="C40" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D40" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E40" t="s">
         <v>58</v>
@@ -12612,16 +11183,16 @@
     </row>
     <row r="41" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
       <c r="B41" t="s">
         <v>134</v>
       </c>
       <c r="C41" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D41" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E41" t="s">
         <v>58</v>
@@ -12635,16 +11206,16 @@
     </row>
     <row r="42" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="B42" t="s">
         <v>135</v>
       </c>
       <c r="C42" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D42" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E42" t="s">
         <v>58</v>
@@ -12658,16 +11229,16 @@
     </row>
     <row r="43" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>435</v>
+        <v>418</v>
       </c>
       <c r="B43" t="s">
         <v>136</v>
       </c>
       <c r="C43" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D43" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E43" t="s">
         <v>58</v>
@@ -12681,16 +11252,16 @@
     </row>
     <row r="44" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s">
         <v>137</v>
       </c>
       <c r="C44" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D44" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E44" t="s">
         <v>58</v>
@@ -12704,16 +11275,16 @@
     </row>
     <row r="45" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
       <c r="B45" t="s">
         <v>138</v>
       </c>
       <c r="C45" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D45" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E45" t="s">
         <v>58</v>
@@ -12727,16 +11298,16 @@
     </row>
     <row r="46" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>436</v>
+        <v>419</v>
       </c>
       <c r="B46" t="s">
         <v>139</v>
       </c>
       <c r="C46" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D46" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E46" t="s">
         <v>58</v>
@@ -12750,16 +11321,16 @@
     </row>
     <row r="47" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>437</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s">
         <v>140</v>
       </c>
       <c r="C47" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D47" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E47" t="s">
         <v>58</v>
@@ -12773,16 +11344,16 @@
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>438</v>
+        <v>421</v>
       </c>
       <c r="B48" t="s">
         <v>141</v>
       </c>
       <c r="C48" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D48" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E48" t="s">
         <v>58</v>
@@ -12796,16 +11367,16 @@
     </row>
     <row r="49" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
       <c r="B49" t="s">
         <v>142</v>
       </c>
       <c r="C49" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D49" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E49" t="s">
         <v>58</v>
@@ -12819,16 +11390,16 @@
     </row>
     <row r="50" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>439</v>
+        <v>422</v>
       </c>
       <c r="B50" t="s">
         <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D50" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E50" t="s">
         <v>58</v>
@@ -12842,16 +11413,16 @@
     </row>
     <row r="51" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="B51" t="s">
         <v>144</v>
       </c>
       <c r="C51" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D51" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E51" t="s">
         <v>58</v>
@@ -12865,16 +11436,16 @@
     </row>
     <row r="52" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B52" t="s">
         <v>145</v>
       </c>
       <c r="C52" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D52" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E52" t="s">
         <v>58</v>
@@ -12888,16 +11459,16 @@
     </row>
     <row r="53" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="B53" t="s">
         <v>146</v>
       </c>
       <c r="C53" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D53" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E53" t="s">
         <v>58</v>
@@ -12911,16 +11482,16 @@
     </row>
     <row r="54" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="B54" t="s">
         <v>147</v>
       </c>
       <c r="C54" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D54" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E54" t="s">
         <v>61</v>
@@ -12934,16 +11505,16 @@
     </row>
     <row r="55" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="B55" t="s">
         <v>148</v>
       </c>
       <c r="C55" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D55" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E55" t="s">
         <v>61</v>
@@ -12957,16 +11528,16 @@
     </row>
     <row r="56" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>440</v>
+        <v>423</v>
       </c>
       <c r="B56" t="s">
         <v>149</v>
       </c>
       <c r="C56" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D56" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E56" t="s">
         <v>61</v>
@@ -12980,16 +11551,16 @@
     </row>
     <row r="57" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>441</v>
+        <v>424</v>
       </c>
       <c r="B57" t="s">
         <v>150</v>
       </c>
       <c r="C57" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D57" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E57" t="s">
         <v>61</v>
@@ -13003,16 +11574,16 @@
     </row>
     <row r="58" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>442</v>
+        <v>425</v>
       </c>
       <c r="B58" t="s">
         <v>151</v>
       </c>
       <c r="C58" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D58" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E58" t="s">
         <v>61</v>
@@ -13026,16 +11597,16 @@
     </row>
     <row r="59" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="B59" t="s">
         <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D59" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E59" t="s">
         <v>61</v>
@@ -13049,16 +11620,16 @@
     </row>
     <row r="60" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>443</v>
+        <v>426</v>
       </c>
       <c r="B60" t="s">
         <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D60" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E60" t="s">
         <v>61</v>
@@ -13072,16 +11643,16 @@
     </row>
     <row r="61" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="B61" t="s">
         <v>154</v>
       </c>
       <c r="C61" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D61" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E61" t="s">
         <v>61</v>
@@ -13095,16 +11666,16 @@
     </row>
     <row r="62" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
       <c r="B62" t="s">
         <v>155</v>
       </c>
       <c r="C62" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D62" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
@@ -13118,16 +11689,16 @@
     </row>
     <row r="63" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="B63" t="s">
         <v>156</v>
       </c>
       <c r="C63" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D63" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
@@ -13141,16 +11712,16 @@
     </row>
     <row r="64" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
       <c r="B64" t="s">
         <v>157</v>
       </c>
       <c r="C64" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D64" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E64" t="s">
         <v>61</v>
@@ -13164,16 +11735,16 @@
     </row>
     <row r="65" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
       <c r="B65" t="s">
         <v>158</v>
       </c>
       <c r="C65" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D65" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E65" t="s">
         <v>61</v>
@@ -13187,16 +11758,16 @@
     </row>
     <row r="66" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B66" t="s">
         <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D66" t="s">
-        <v>412</v>
+        <v>395</v>
       </c>
       <c r="E66" t="s">
         <v>61</v>
@@ -13210,16 +11781,16 @@
     </row>
     <row r="67" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s">
         <v>160</v>
       </c>
       <c r="C67" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
       <c r="D67" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E67" t="s">
         <v>60</v>
@@ -13233,16 +11804,16 @@
     </row>
     <row r="68" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="B68" t="s">
         <v>161</v>
       </c>
       <c r="C68" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D68" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E68" t="s">
         <v>60</v>
@@ -13256,16 +11827,16 @@
     </row>
     <row r="69" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
       <c r="B69" t="s">
         <v>162</v>
       </c>
       <c r="C69" t="s">
-        <v>405</v>
+        <v>388</v>
       </c>
       <c r="D69" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E69" t="s">
         <v>60</v>
@@ -13279,16 +11850,16 @@
     </row>
     <row r="70" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>338</v>
+        <v>321</v>
       </c>
       <c r="B70" t="s">
         <v>163</v>
       </c>
       <c r="C70" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D70" t="s">
-        <v>410</v>
+        <v>393</v>
       </c>
       <c r="E70" t="s">
         <v>60</v>
@@ -13302,19 +11873,19 @@
     </row>
     <row r="71" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
       <c r="B71" t="s">
         <v>164</v>
       </c>
       <c r="C71" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D71" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E71" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="F71">
         <v>63</v>
@@ -13325,19 +11896,19 @@
     </row>
     <row r="72" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="B72" t="s">
         <v>165</v>
       </c>
       <c r="C72" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D72" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E72" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F72">
         <v>15</v>
@@ -13348,19 +11919,19 @@
     </row>
     <row r="73" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>341</v>
+        <v>324</v>
       </c>
       <c r="B73" t="s">
         <v>166</v>
       </c>
       <c r="C73" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D73" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E73" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F73">
         <v>14</v>
@@ -13371,19 +11942,19 @@
     </row>
     <row r="74" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
       <c r="B74" t="s">
         <v>167</v>
       </c>
       <c r="C74" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D74" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E74" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F74">
         <v>25</v>
@@ -13394,19 +11965,19 @@
     </row>
     <row r="75" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
       <c r="B75" t="s">
         <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D75" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E75" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F75">
         <v>61</v>
@@ -13417,19 +11988,19 @@
     </row>
     <row r="76" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
       <c r="B76" t="s">
         <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="D76" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E76" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F76">
         <v>45</v>
@@ -13440,19 +12011,19 @@
     </row>
     <row r="77" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
       <c r="B77" t="s">
         <v>170</v>
       </c>
       <c r="C77" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D77" t="s">
-        <v>407</v>
+        <v>390</v>
       </c>
       <c r="E77" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="F77">
         <v>44</v>
@@ -13463,19 +12034,19 @@
     </row>
     <row r="78" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
       <c r="B78" t="s">
         <v>171</v>
       </c>
       <c r="C78" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D78" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E78" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F78">
         <v>56</v>
@@ -13486,19 +12057,19 @@
     </row>
     <row r="79" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="B79" t="s">
         <v>172</v>
       </c>
       <c r="C79" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D79" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E79" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F79">
         <v>78</v>
@@ -13509,19 +12080,19 @@
     </row>
     <row r="80" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="B80" t="s">
         <v>173</v>
       </c>
       <c r="C80" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
       <c r="D80" t="s">
-        <v>413</v>
+        <v>396</v>
       </c>
       <c r="E80" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="F80">
         <v>212</v>
@@ -13532,19 +12103,19 @@
     </row>
     <row r="81" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
       <c r="B81" t="s">
         <v>174</v>
       </c>
       <c r="C81" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="D81" t="s">
-        <v>415</v>
+        <v>398</v>
       </c>
       <c r="E81" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="F81">
         <v>51</v>
@@ -13555,16 +12126,16 @@
     </row>
     <row r="82" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
       <c r="B82" t="s">
         <v>175</v>
       </c>
       <c r="C82" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D82" t="s">
-        <v>414</v>
+        <v>397</v>
       </c>
       <c r="E82" t="s">
         <v>59</v>
@@ -13578,16 +12149,16 @@
     </row>
     <row r="83" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
       <c r="B83" t="s">
         <v>176</v>
       </c>
       <c r="C83" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D83" t="s">
-        <v>416</v>
+        <v>399</v>
       </c>
       <c r="E83" t="s">
         <v>57</v>
@@ -13601,16 +12172,16 @@
     </row>
     <row r="84" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
       <c r="B84" t="s">
         <v>177</v>
       </c>
       <c r="C84" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D84" t="s">
-        <v>417</v>
+        <v>400</v>
       </c>
       <c r="E84" t="s">
         <v>56</v>
@@ -13624,19 +12195,19 @@
     </row>
     <row r="85" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>455</v>
+        <v>438</v>
       </c>
       <c r="B85" t="s">
         <v>178</v>
       </c>
       <c r="C85" t="s">
-        <v>406</v>
+        <v>389</v>
       </c>
       <c r="D85" t="s">
-        <v>418</v>
+        <v>401</v>
       </c>
       <c r="E85" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F85">
         <v>72</v>
@@ -13647,16 +12218,16 @@
     </row>
     <row r="86" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="B86" t="s">
         <v>179</v>
       </c>
       <c r="C86" t="s">
-        <v>404</v>
+        <v>387</v>
       </c>
       <c r="D86" t="s">
-        <v>419</v>
+        <v>402</v>
       </c>
       <c r="E86" t="s">
         <v>59</v>
@@ -13670,16 +12241,16 @@
     </row>
     <row r="87" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="B87" t="s">
         <v>180</v>
       </c>
       <c r="C87" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="D87" t="s">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="E87" t="s">
         <v>59</v>
@@ -14609,4 +13180,1957 @@
   <pageSetup orientation="landscape"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:C1006"/>
+  <sheetFormatPr defaultColWidth="12.625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.625" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="7.625" customWidth="1"/>
+    <col min="4" max="26" width="8.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C3" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="str">
+        <f>A3</f>
+        <v>BiID0002</v>
+      </c>
+      <c r="B4" t="s">
+        <v>322</v>
+      </c>
+      <c r="C4" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B6" t="s">
+        <v>324</v>
+      </c>
+      <c r="C6" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C8" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="str">
+        <f>A8</f>
+        <v>BiID0003</v>
+      </c>
+      <c r="B9" t="s">
+        <v>327</v>
+      </c>
+      <c r="C9" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B10" t="s">
+        <v>328</v>
+      </c>
+      <c r="C10" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B11" t="s">
+        <v>329</v>
+      </c>
+      <c r="C11" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B12" t="s">
+        <v>330</v>
+      </c>
+      <c r="C12" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B13" t="s">
+        <v>331</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="str">
+        <f>A12</f>
+        <v>BiID0005</v>
+      </c>
+      <c r="B14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B15" t="s">
+        <v>333</v>
+      </c>
+      <c r="C15" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B16" t="s">
+        <v>334</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B17" t="s">
+        <v>324</v>
+      </c>
+      <c r="C17" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B18" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B19" t="s">
+        <v>336</v>
+      </c>
+      <c r="C19" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B22" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B23" t="s">
+        <v>339</v>
+      </c>
+      <c r="C23" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B24" t="s">
+        <v>340</v>
+      </c>
+      <c r="C24" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B25" t="s">
+        <v>331</v>
+      </c>
+      <c r="C25" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B26" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B27" t="s">
+        <v>341</v>
+      </c>
+      <c r="C27" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B28" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B29" t="s">
+        <v>327</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" t="s">
+        <v>343</v>
+      </c>
+      <c r="C30" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B31" t="s">
+        <v>344</v>
+      </c>
+      <c r="C31" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" t="s">
+        <v>336</v>
+      </c>
+      <c r="C32" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B33" t="s">
+        <v>345</v>
+      </c>
+      <c r="C33" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B34" t="s">
+        <v>346</v>
+      </c>
+      <c r="C34" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B35" t="s">
+        <v>347</v>
+      </c>
+      <c r="C35" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B36" t="s">
+        <v>348</v>
+      </c>
+      <c r="C36" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B37" t="s">
+        <v>349</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+      <c r="C38" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B39" t="s">
+        <v>351</v>
+      </c>
+      <c r="C39" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B40" t="s">
+        <v>352</v>
+      </c>
+      <c r="C40" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B41" t="s">
+        <v>353</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B42" t="s">
+        <v>354</v>
+      </c>
+      <c r="C42" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B43" t="s">
+        <v>355</v>
+      </c>
+      <c r="C43" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B44" t="s">
+        <v>356</v>
+      </c>
+      <c r="C44" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" t="s">
+        <v>344</v>
+      </c>
+      <c r="C45" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B46" t="s">
+        <v>357</v>
+      </c>
+      <c r="C46" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B47" t="s">
+        <v>346</v>
+      </c>
+      <c r="C47" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B48" t="s">
+        <v>354</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B49" t="s">
+        <v>358</v>
+      </c>
+      <c r="C49" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B50" t="s">
+        <v>336</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B51" t="s">
+        <v>359</v>
+      </c>
+      <c r="C51" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B52" t="s">
+        <v>360</v>
+      </c>
+      <c r="C52" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B53" t="s">
+        <v>323</v>
+      </c>
+      <c r="C53" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" t="s">
+        <v>361</v>
+      </c>
+      <c r="C54" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C55" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C56" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C57" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C58" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="C59" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C60" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C61" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="C62" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C63" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C66" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C67" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C68" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C69" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C70" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="C71" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="C72" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="C73" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C74" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="C75" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="4" t="str">
+        <f>A77</f>
+        <v>BiID0039</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C76" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C77" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C78" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="C79" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="C80" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B81" s="1"/>
+    </row>
+    <row r="82" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="4"/>
+      <c r="B82" s="1"/>
+    </row>
+    <row r="83" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+    </row>
+    <row r="84" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+    </row>
+    <row r="85" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+    </row>
+    <row r="86" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+    </row>
+    <row r="87" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+    </row>
+    <row r="88" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="1"/>
+      <c r="B88" s="1"/>
+    </row>
+    <row r="89" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="1"/>
+      <c r="B89" s="1"/>
+    </row>
+    <row r="90" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="1"/>
+      <c r="B90" s="1"/>
+    </row>
+    <row r="91" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="1"/>
+      <c r="B91" s="1"/>
+    </row>
+    <row r="92" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="1"/>
+      <c r="B92" s="1"/>
+    </row>
+    <row r="93" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="1"/>
+      <c r="B93" s="1"/>
+    </row>
+    <row r="94" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="1"/>
+      <c r="B94" s="1"/>
+    </row>
+    <row r="95" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="1"/>
+      <c r="B95" s="1"/>
+    </row>
+    <row r="96" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="1"/>
+      <c r="B96" s="1"/>
+    </row>
+    <row r="97" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B97" s="1"/>
+    </row>
+    <row r="98" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B98" s="1"/>
+    </row>
+    <row r="99" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B99" s="1"/>
+    </row>
+    <row r="100" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B101" s="1"/>
+    </row>
+    <row r="102" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B102" s="1"/>
+    </row>
+    <row r="103" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B103" s="1"/>
+    </row>
+    <row r="104" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B104" s="1"/>
+    </row>
+    <row r="105" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B105" s="1"/>
+    </row>
+    <row r="106" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B106" s="1"/>
+    </row>
+    <row r="107" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B107" s="1"/>
+    </row>
+    <row r="108" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B108" s="1"/>
+    </row>
+    <row r="109" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B109" s="1"/>
+    </row>
+    <row r="110" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B110" s="1"/>
+    </row>
+    <row r="111" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B111" s="1"/>
+    </row>
+    <row r="112" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B112" s="1"/>
+    </row>
+    <row r="113" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B113" s="1"/>
+    </row>
+    <row r="114" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B114" s="1"/>
+    </row>
+    <row r="115" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B115" s="1"/>
+    </row>
+    <row r="116" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B116" s="1"/>
+    </row>
+    <row r="117" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B117" s="1"/>
+    </row>
+    <row r="118" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B118" s="1"/>
+    </row>
+    <row r="119" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B119" s="1"/>
+    </row>
+    <row r="120" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B120" s="1"/>
+    </row>
+    <row r="121" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B121" s="1"/>
+    </row>
+    <row r="122" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B122" s="1"/>
+    </row>
+    <row r="123" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="1"/>
+    </row>
+    <row r="124" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="1"/>
+    </row>
+    <row r="125" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="1"/>
+    </row>
+    <row r="126" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="1"/>
+    </row>
+    <row r="127" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B128" s="1"/>
+    </row>
+    <row r="129" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B129" s="1"/>
+    </row>
+    <row r="130" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B130" s="1"/>
+    </row>
+    <row r="131" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B131" s="1"/>
+    </row>
+    <row r="132" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B132" s="1"/>
+    </row>
+    <row r="133" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B133" s="1"/>
+    </row>
+    <row r="134" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="135" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="136" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="137" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="138" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="139" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="140" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="142" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="143" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="144" spans="2:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="145" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="146" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="147" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="149" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="150" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="151" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="152" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="153" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="154" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="155" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="156" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="157" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="158" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="159" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="160" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="161" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="162" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="163" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="164" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="166" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="167" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="168" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="169" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="170" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="171" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="172" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="173" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="174" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="175" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="176" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="177" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="178" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="179" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="180" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="181" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="182" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="183" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="184" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="185" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="186" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="187" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="188" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="189" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="190" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="191" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="192" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="193" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="194" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="195" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="196" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="197" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="198" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="199" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="200" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="202" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="203" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="204" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="205" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="207" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="208" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="210" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="212" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="213" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="214" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="215" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="216" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="218" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="219" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="220" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="221" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="222" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="224" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="225" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="226" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="227" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="229" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="230" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="231" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="232" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="233" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="234" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="235" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="236" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="237" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="238" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="239" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="240" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="241" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="242" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="243" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="244" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="245" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="246" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="247" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="248" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="249" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="250" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="251" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="252" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="253" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="254" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="255" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="256" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="257" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="258" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="259" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="266" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="267" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="268" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="269" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="270" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="271" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="272" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="273" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="274" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="275" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="276" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="277" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="278" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="279" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="280" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="281" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="282" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="283" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="284" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="285" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="286" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="290" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="291" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="302" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="303" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="304" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="305" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="306" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="307" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="308" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="309" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="310" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="311" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="312" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="313" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="314" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="315" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="316" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="317" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="318" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="319" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="320" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="321" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="322" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="323" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="324" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="325" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="326" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="327" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="328" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="329" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="330" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="333" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="334" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="335" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="336" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="337" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="338" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="339" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="340" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="341" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="342" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="343" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="344" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="345" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="346" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="347" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="348" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="349" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="350" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="351" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="352" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="353" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="354" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="355" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="356" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="357" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="358" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="359" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="360" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="361" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="362" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="363" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="364" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="365" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="366" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="367" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="368" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="369" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="370" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="371" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="372" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="373" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="374" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="375" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="376" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="377" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="378" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="379" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="380" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="381" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="382" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="383" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="384" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="385" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="386" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="387" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="388" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="389" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="390" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="391" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="392" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="393" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="394" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="395" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="396" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="397" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="398" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="399" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="400" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="401" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="402" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="403" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="404" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="405" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="406" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="407" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="408" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="409" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="410" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="411" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="412" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="413" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="414" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="415" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="416" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="417" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="418" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="419" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="420" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="421" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="422" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="423" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="424" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="425" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="426" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="427" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="428" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="429" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="430" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="431" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="432" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="433" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="434" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="435" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="436" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="437" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="438" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="439" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="440" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="441" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="442" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="443" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="444" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="445" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="446" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="447" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="448" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="449" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="450" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="451" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="452" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="453" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="454" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="455" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="456" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="457" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="458" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="459" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="460" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="461" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="462" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="463" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="464" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="465" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="466" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="467" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="468" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="469" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="470" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="471" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="472" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="473" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="474" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="475" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="476" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="477" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="478" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="479" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="480" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="481" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="482" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="483" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="484" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="485" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="486" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="487" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="488" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="489" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="490" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="491" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="492" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="493" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="494" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="495" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="496" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="500" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="501" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="502" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="503" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="504" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="505" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="506" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="507" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="508" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="509" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="510" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="511" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="512" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="513" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="514" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="515" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="516" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="517" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="518" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="519" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="520" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="521" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="522" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="523" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="524" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="525" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="526" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="527" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="528" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="529" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="530" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="531" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="532" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="533" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="534" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="535" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="536" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="537" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="538" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="539" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="540" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="541" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="542" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="543" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="544" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="545" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="546" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="547" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="548" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="549" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="550" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="551" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="552" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="553" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="554" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="555" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="556" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="557" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="558" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="559" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="560" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="561" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="562" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="563" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="564" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="565" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="566" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="567" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="568" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="569" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="570" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="571" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="572" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="573" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="574" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="575" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="576" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="577" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="578" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="579" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="580" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="581" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="582" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="583" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="584" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="585" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="586" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="587" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="588" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="589" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="590" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="591" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="592" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="593" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="594" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="595" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="596" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="597" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="598" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="599" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="600" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="601" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="602" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="603" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="604" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="605" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="606" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="607" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="608" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="609" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="610" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="611" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="612" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="613" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="614" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="615" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="616" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="617" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="618" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="619" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="620" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="621" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="622" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="623" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="624" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="625" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="626" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="627" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="628" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="629" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="630" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="631" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="632" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="633" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="634" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="635" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="636" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="637" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="638" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="639" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="640" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="641" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="642" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="643" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="644" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="645" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="646" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="647" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="648" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="649" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="650" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="651" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="652" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="653" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="654" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="655" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="656" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="657" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="658" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="659" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="660" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="661" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="662" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="663" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="664" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="665" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="666" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="667" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="668" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="669" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="670" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="671" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="672" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="673" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="674" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="675" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="676" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="677" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="678" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="679" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="680" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="681" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="682" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="683" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="684" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="685" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="686" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="687" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="688" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="689" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="690" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="691" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="692" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="693" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="694" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="695" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="696" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="697" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="698" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="699" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="700" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="701" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="702" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="703" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="704" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="705" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="706" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="707" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="708" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="709" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="710" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="711" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="712" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="713" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="714" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="715" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="716" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="717" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="718" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="719" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="720" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="721" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="722" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="723" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="724" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="725" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="726" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="727" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="728" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="729" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="730" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="731" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="732" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="733" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="734" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="735" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="736" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="737" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="738" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="739" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="740" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="741" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="742" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="743" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="744" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="745" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="746" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="747" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="748" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="749" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="750" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="751" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="752" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="753" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="754" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="755" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="756" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="758" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="759" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="760" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="761" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="762" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="763" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="764" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="765" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="766" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="767" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="768" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="769" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="770" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="771" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="772" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="773" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="774" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="775" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="776" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="777" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="778" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="779" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="780" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="781" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="782" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="783" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="784" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="785" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="786" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="787" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="788" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="789" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="790" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="791" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="792" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="793" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="794" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="795" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="796" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="797" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="798" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="799" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="800" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="801" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="802" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="803" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="804" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="805" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="806" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="807" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="808" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="809" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="810" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="811" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="812" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="813" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="814" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="815" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="816" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="817" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="818" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="819" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="820" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="821" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="822" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="823" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="824" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="825" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="826" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="827" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="828" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="829" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="830" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="831" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="832" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="833" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="834" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="835" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="836" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="837" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="838" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="839" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="840" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="841" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="842" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="843" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="844" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="845" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="846" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="847" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="848" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="849" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="850" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="851" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="852" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="853" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="854" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="855" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="856" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="857" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="858" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="859" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="860" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="861" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="862" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="863" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="864" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="865" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="866" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="867" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="868" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="869" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="870" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="871" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="872" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="873" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="874" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="875" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="876" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="877" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="878" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="879" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="880" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="881" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="882" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="883" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="884" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="885" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="886" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="887" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="888" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="889" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="890" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="891" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="892" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="893" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="894" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="895" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="896" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="897" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="898" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="899" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="900" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="901" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="902" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="903" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="904" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="905" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="906" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="907" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="908" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="909" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="910" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="911" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="912" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="913" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="914" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="915" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="916" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="917" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="918" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="919" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="920" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="921" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="922" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="923" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="924" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="925" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="926" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="927" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="928" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="929" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="930" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="931" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="932" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="933" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="934" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="935" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="936" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="937" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="938" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="939" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="940" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="941" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="942" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="943" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="944" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="945" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="946" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="947" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="948" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="949" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="950" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="951" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="952" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="953" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="954" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="955" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="956" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="957" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="958" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="959" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="960" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="961" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="962" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="963" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="964" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="965" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="966" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="967" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="968" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="969" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="970" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="971" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="972" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="973" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="974" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="975" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="976" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="977" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="978" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="979" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="980" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="981" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="982" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="983" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="984" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="985" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="986" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="987" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="988" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="989" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="990" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="991" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="992" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="993" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="994" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="995" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="996" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="997" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="998" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="999" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1001" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1002" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1003" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1004" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1005" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="1006" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A80">
+    <sortCondition ref="A2:A80"/>
+  </sortState>
+  <phoneticPr fontId="14" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
 </file>